--- a/output/yearly_surface_area_iteration_59_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_59_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497596250442</v>
+        <v>10.84497625220732</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907065366125</v>
+        <v>37.78907166312434</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.040112787153877</v>
+        <v>5.882632243846888</v>
       </c>
       <c r="C2" t="n">
-        <v>15.34569836508189</v>
+        <v>9.451285148784043</v>
       </c>
       <c r="D2" t="n">
-        <v>26.30298449218055</v>
+        <v>20.70113209174824</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.47020039707199</v>
+        <v>17.11186248502191</v>
       </c>
       <c r="C3" t="n">
-        <v>37.69420310455629</v>
+        <v>22.85999529338698</v>
       </c>
       <c r="D3" t="n">
-        <v>61.79610924381548</v>
+        <v>71.29451828240336</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.35197406640165</v>
+        <v>33.88502201207866</v>
       </c>
       <c r="C4" t="n">
-        <v>58.19800390775092</v>
+        <v>54.7265440255342</v>
       </c>
       <c r="D4" t="n">
-        <v>81.01774754526377</v>
+        <v>86.48019177169304</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.16101629015904</v>
+        <v>43.04963683122264</v>
       </c>
       <c r="C5" t="n">
-        <v>112.7046364475339</v>
+        <v>95.30315838975913</v>
       </c>
       <c r="D5" t="n">
-        <v>62.41461029749098</v>
+        <v>57.72676500971247</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.28311285838414</v>
+        <v>43.23027840880406</v>
       </c>
       <c r="C6" t="n">
-        <v>158.5915241440298</v>
+        <v>100.0656165030604</v>
       </c>
       <c r="D6" t="n">
-        <v>45.92713935237005</v>
+        <v>41.82147045320988</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.70375853969149</v>
+        <v>30.48228446915921</v>
       </c>
       <c r="C7" t="n">
-        <v>162.4124862089583</v>
+        <v>84.08080038251383</v>
       </c>
       <c r="D7" t="n">
-        <v>38.92629647338602</v>
+        <v>38.08788393395925</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.0207398749762</v>
+        <v>16.02212253330794</v>
       </c>
       <c r="C8" t="n">
-        <v>112.8224461720434</v>
+        <v>63.50435024920493</v>
       </c>
       <c r="D8" t="n">
-        <v>35.71598148049896</v>
+        <v>36.38356991938679</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.432811868852599</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>56.13437023342411</v>
+        <v>40.82499653339935</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>34.05780960802609</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>28.43141351498762</v>
+        <v>29.67528785626833</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>26.90381408717959</v>
+        <v>28.20561154301086</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>24.71549845441346</v>
+        <v>26.27647730416588</v>
       </c>
       <c r="D13" t="n">
         <v>32.5203927031756</v>
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.18589447346791</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.640595955730071</v>
+        <v>7.713870808805265</v>
       </c>
       <c r="C21" t="n">
-        <v>92.64222596322711</v>
+        <v>96.42338511006581</v>
       </c>
       <c r="D21" t="n">
-        <v>7.640595955730071</v>
+        <v>8.678104659905923</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.65174160689964</v>
+        <v>7.370961763485052</v>
       </c>
       <c r="C2" t="n">
-        <v>20.38500933098077</v>
+        <v>7.268860002243384</v>
       </c>
       <c r="D2" t="n">
-        <v>22.90319219237384</v>
+        <v>25.02965771977243</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.34181243199391</v>
+        <v>18.42740440871263</v>
       </c>
       <c r="C3" t="n">
-        <v>48.02709769175397</v>
+        <v>30.18874190558942</v>
       </c>
       <c r="D3" t="n">
-        <v>66.66557785687966</v>
+        <v>71.0245376637355</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.33997210977243</v>
+        <v>33.04268248183489</v>
       </c>
       <c r="C4" t="n">
-        <v>74.38113306455534</v>
+        <v>55.93900244027901</v>
       </c>
       <c r="D4" t="n">
-        <v>90.0027025345306</v>
+        <v>100.9275909873891</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.47441479199203</v>
+        <v>47.17297718905925</v>
       </c>
       <c r="C5" t="n">
-        <v>108.9249077861836</v>
+        <v>97.16847902782808</v>
       </c>
       <c r="D5" t="n">
-        <v>74.8582624488193</v>
+        <v>73.11566027378122</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.33973543006097</v>
+        <v>50.4353248102714</v>
       </c>
       <c r="C6" t="n">
-        <v>168.4129281773149</v>
+        <v>125.4644113596297</v>
       </c>
       <c r="D6" t="n">
-        <v>52.97117913034091</v>
+        <v>49.87180162803373</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.48334833232147</v>
+        <v>40.60312155223958</v>
       </c>
       <c r="C7" t="n">
-        <v>191.6970384789364</v>
+        <v>113.0659196026967</v>
       </c>
       <c r="D7" t="n">
-        <v>42.81892612072463</v>
+        <v>41.44153409166636</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.28076414788136</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="C8" t="n">
-        <v>159.4701883393306</v>
+        <v>87.62098260402782</v>
       </c>
       <c r="D8" t="n">
-        <v>37.46840113257952</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>11.6484365108884</v>
       </c>
       <c r="C9" t="n">
-        <v>92.2999921624681</v>
+        <v>59.12968247908112</v>
       </c>
       <c r="D9" t="n">
-        <v>35.16718451382499</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>6.548257187326225</v>
       </c>
       <c r="C10" t="n">
-        <v>47.54604131667303</v>
+        <v>40.00131020953629</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>30.8092064546734</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.0569667290421</v>
+        <v>28.87810872041993</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>24.58296251434014</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.809834822785591</v>
+        <v>7.902516349917921</v>
       </c>
       <c r="C21" t="n">
-        <v>100.5516233433645</v>
+        <v>105.6961561801522</v>
       </c>
       <c r="D21" t="n">
-        <v>8.78606417563379</v>
+        <v>9.8781454373974</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.433212779480101</v>
+        <v>8.963356539773379</v>
       </c>
       <c r="C2" t="n">
-        <v>17.37693436516854</v>
+        <v>7.162831250184728</v>
       </c>
       <c r="D2" t="n">
-        <v>20.73451151369263</v>
+        <v>30.34582153826891</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.10895829963817</v>
+        <v>21.21065915025234</v>
       </c>
       <c r="C3" t="n">
-        <v>61.33959656134072</v>
+        <v>29.31498644880976</v>
       </c>
       <c r="D3" t="n">
-        <v>68.13819941324986</v>
+        <v>73.29237486054562</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.78666731520473</v>
+        <v>33.77015753068178</v>
       </c>
       <c r="C4" t="n">
-        <v>92.95089089038376</v>
+        <v>64.41344862333747</v>
       </c>
       <c r="D4" t="n">
-        <v>99.25567464705678</v>
+        <v>109.7466306146382</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.7443954106599</v>
+        <v>48.03200643027521</v>
       </c>
       <c r="C5" t="n">
-        <v>120.4113559258713</v>
+        <v>98.78836273983532</v>
       </c>
       <c r="D5" t="n">
-        <v>85.04389488037997</v>
+        <v>89.46175954949061</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.37748381117885</v>
+        <v>56.27181491201868</v>
       </c>
       <c r="C6" t="n">
-        <v>169.2582129506714</v>
+        <v>138.9084644215855</v>
       </c>
       <c r="D6" t="n">
-        <v>61.62528514327655</v>
+        <v>58.80766923208819</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>49.70588626601601</v>
+        <v>49.34656660626167</v>
       </c>
       <c r="C7" t="n">
-        <v>212.2381456948924</v>
+        <v>142.8894513623063</v>
       </c>
       <c r="D7" t="n">
-        <v>46.53189593818607</v>
+        <v>45.8132566186774</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>30.54217107911827</v>
+        <v>33.37942194439155</v>
       </c>
       <c r="C8" t="n">
-        <v>199.4420461177395</v>
+        <v>116.3272854762046</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>39.97185777840888</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.08749871886498</v>
+        <v>17.19531103988288</v>
       </c>
       <c r="C9" t="n">
-        <v>133.568738658187</v>
+        <v>80.98436812331937</v>
       </c>
       <c r="D9" t="n">
-        <v>36.16562192904399</v>
+        <v>37.38593432542277</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.687084524252525</v>
+        <v>8.541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>71.31906197500955</v>
+        <v>53.24017800130454</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>5.508586368528851</v>
       </c>
       <c r="C11" t="n">
-        <v>41.04785326226338</v>
+        <v>39.27088991757665</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.54493639578176</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.13827186204534</v>
+        <v>31.47974013667398</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>33.82120841130262</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>26.42668470291564</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.69215749368978</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.962182390383933</v>
+        <v>8.075947208229536</v>
       </c>
       <c r="C21" t="n">
-        <v>107.4894622701831</v>
+        <v>114.0727543162422</v>
       </c>
       <c r="D21" t="n">
-        <v>9.952727987979916</v>
+        <v>11.10442741131561</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.80882123957913</v>
+        <v>8.047385931711105</v>
       </c>
       <c r="C2" t="n">
-        <v>12.23257639491526</v>
+        <v>4.75558587937155</v>
       </c>
       <c r="D2" t="n">
-        <v>17.24145318198248</v>
+        <v>24.59670698219958</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.2849121228766</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="C3" t="n">
-        <v>82.66806543610267</v>
+        <v>42.76002125846983</v>
       </c>
       <c r="D3" t="n">
-        <v>74.23485265662258</v>
+        <v>81.3181623427633</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.33399950808894</v>
+        <v>23.07499804061703</v>
       </c>
       <c r="C4" t="n">
-        <v>109.185070927809</v>
+        <v>85.79100488331179</v>
       </c>
       <c r="D4" t="n">
-        <v>94.82701075319942</v>
+        <v>104.3990508696058</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.01755795215198</v>
+        <v>31.68590715456581</v>
       </c>
       <c r="C5" t="n">
-        <v>101.1200135374215</v>
+        <v>82.98222470146166</v>
       </c>
       <c r="D5" t="n">
-        <v>58.8557748695963</v>
+        <v>60.03387211469246</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.83276839957533</v>
+        <v>30.63151012020474</v>
       </c>
       <c r="C6" t="n">
-        <v>139.7940008508161</v>
+        <v>94.10837143369076</v>
       </c>
       <c r="D6" t="n">
-        <v>30.63151012020474</v>
+        <v>30.14849024971531</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.24167416616073</v>
+        <v>22.09815907489146</v>
       </c>
       <c r="C7" t="n">
-        <v>140.2544405241078</v>
+        <v>81.80510920406972</v>
       </c>
       <c r="D7" t="n">
-        <v>28.02693346083794</v>
+        <v>28.086820070797</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>11.93314334511998</v>
       </c>
       <c r="C8" t="n">
-        <v>98.3858461810941</v>
+        <v>59.6657167255999</v>
       </c>
       <c r="D8" t="n">
-        <v>26.62008900065226</v>
+        <v>27.53802310412303</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>54.35937038414588</v>
+        <v>40.60312155223957</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>27.62343515439249</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.558835427894688</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>32.17187226816798</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>28.32833000604172</v>
+        <v>29.32480392585223</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>27.72062817711293</v>
+        <v>28.25371718051895</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>23.64932044760141</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>27.55471281509523</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.6145740628585034</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3583379120500857</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>23.29196428325557</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>15.51652246562084</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.37631247036279</v>
+        <v>14.44641746799181</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>9.628981483252716</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.701589755637975</v>
+        <v>4.844924920458009</v>
       </c>
       <c r="C2" t="n">
-        <v>6.200718500022854</v>
+        <v>2.821542902005333</v>
       </c>
       <c r="D2" t="n">
-        <v>12.42107195413064</v>
+        <v>17.03135917327366</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.51700549170635</v>
+        <v>27.03733177495716</v>
       </c>
       <c r="C3" t="n">
-        <v>66.82756622808039</v>
+        <v>30.60598467989431</v>
       </c>
       <c r="D3" t="n">
-        <v>71.60867754776235</v>
+        <v>83.28165775125693</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.53592073999429</v>
+        <v>34.31895449735575</v>
       </c>
       <c r="C4" t="n">
-        <v>157.7982719989983</v>
+        <v>99.48540360985054</v>
       </c>
       <c r="D4" t="n">
-        <v>107.896036192133</v>
+        <v>119.6632641752352</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.18369429834795</v>
+        <v>34.70478134512475</v>
       </c>
       <c r="C5" t="n">
-        <v>144.6850679133737</v>
+        <v>119.8713946885356</v>
       </c>
       <c r="D5" t="n">
-        <v>72.40389318820228</v>
+        <v>76.91993262773761</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.30699359845555</v>
+        <v>36.87051678069322</v>
       </c>
       <c r="C6" t="n">
-        <v>156.8607029414426</v>
+        <v>113.7914311561351</v>
       </c>
       <c r="D6" t="n">
-        <v>36.8302651248191</v>
+        <v>37.19253002768617</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.68462230722529</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="C7" t="n">
-        <v>167.7423944953142</v>
+        <v>105.5202067478557</v>
       </c>
       <c r="D7" t="n">
-        <v>30.60205768907732</v>
+        <v>30.42239785920016</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.678649705541805</v>
+        <v>9.930378028456486</v>
       </c>
       <c r="C8" t="n">
-        <v>127.7597374921587</v>
+        <v>77.4402589109884</v>
       </c>
       <c r="D8" t="n">
-        <v>27.12078032981814</v>
+        <v>28.78975142703771</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.326562132615692</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
-        <v>57.02187015806322</v>
+        <v>47.59218345877262</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>28.95468504135117</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>29.18245050873644</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.43141351498762</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>19.52696183746906</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.27647730416588</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.70599977254047</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.22217808079604</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>12.27773678931061</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>8.025787482217675</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>65.59743635465912</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.168901662859456</v>
+        <v>5.283766144256333</v>
       </c>
       <c r="C2" t="n">
-        <v>5.468334712654734</v>
+        <v>6.400995031689204</v>
       </c>
       <c r="D2" t="n">
-        <v>11.09080381487622</v>
+        <v>16.8350096324243</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.30392518215579</v>
+        <v>21.65735435568464</v>
       </c>
       <c r="C3" t="n">
-        <v>45.5089148303609</v>
+        <v>19.90002596508285</v>
       </c>
       <c r="D3" t="n">
-        <v>66.18943022031996</v>
+        <v>77.81823177712343</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.44055234396211</v>
+        <v>43.29114676646735</v>
       </c>
       <c r="C4" t="n">
-        <v>161.8568170083547</v>
+        <v>87.28424314147117</v>
       </c>
       <c r="D4" t="n">
-        <v>116.6384994984508</v>
+        <v>132.7578150544792</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.58959806855839</v>
+        <v>42.68148144213009</v>
       </c>
       <c r="C5" t="n">
-        <v>211.7875234986432</v>
+        <v>153.4962535589888</v>
       </c>
       <c r="D5" t="n">
-        <v>88.94634200476104</v>
+        <v>99.57376090323277</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.62650357069227</v>
+        <v>41.94222542083224</v>
       </c>
       <c r="C6" t="n">
-        <v>189.384040887731</v>
+        <v>150.7827029044506</v>
       </c>
       <c r="D6" t="n">
-        <v>48.10072876957248</v>
+        <v>50.35482149852316</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.5478405811655</v>
+        <v>30.78171751895449</v>
       </c>
       <c r="C7" t="n">
-        <v>196.3083074457837</v>
+        <v>135.2239652875472</v>
       </c>
       <c r="D7" t="n">
-        <v>33.89582123682538</v>
+        <v>33.71616140694821</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.60073178400781</v>
+        <v>14.85384276525424</v>
       </c>
       <c r="C8" t="n">
-        <v>169.4005663677871</v>
+        <v>107.4817386609408</v>
       </c>
       <c r="D8" t="n">
-        <v>28.62285431731576</v>
+        <v>30.62561963397925</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>6.767186925373262</v>
       </c>
       <c r="C9" t="n">
-        <v>97.29217923856312</v>
+        <v>70.11249404649018</v>
       </c>
       <c r="D9" t="n">
-        <v>28.84374755077128</v>
+        <v>29.7312474754104</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>2.847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>47.11898106532567</v>
+        <v>43.2754388031994</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>30.89069151412589</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>34.82848155585983</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>23.64932044760141</v>
+        <v>26.03594911662541</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.07347651356504</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.21141991377833</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>20.28094407433061</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.69185439405351</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.38885420633975</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.09962384868121</v>
+        <v>35.50686921949439</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.16417285078747</v>
+        <v>3.100359250011427</v>
       </c>
       <c r="C2" t="n">
-        <v>2.698824438974482</v>
+        <v>2.894192232119597</v>
       </c>
       <c r="D2" t="n">
-        <v>7.86085386790421</v>
+        <v>11.59444038715483</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.52972715413255</v>
+        <v>22.02060100625596</v>
       </c>
       <c r="C3" t="n">
-        <v>38.67104207028186</v>
+        <v>23.48831382410494</v>
       </c>
       <c r="D3" t="n">
-        <v>63.77923960639404</v>
+        <v>76.6597694861122</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.30765655099029</v>
+        <v>47.97506506342888</v>
       </c>
       <c r="C4" t="n">
-        <v>161.0655283587317</v>
+        <v>81.55378179178254</v>
       </c>
       <c r="D4" t="n">
-        <v>123.8366736659884</v>
+        <v>141.7682954840564</v>
       </c>
     </row>
     <row r="5">
@@ -2691,10 +2691,10 @@
         <v>44.93950116189775</v>
       </c>
       <c r="C5" t="n">
-        <v>263.0347536603267</v>
+        <v>179.3162181806799</v>
       </c>
       <c r="D5" t="n">
-        <v>91.42525495798422</v>
+        <v>108.3849465488479</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.65038431076368</v>
+        <v>36.54850353370026</v>
       </c>
       <c r="C6" t="n">
-        <v>225.9727960773054</v>
+        <v>186.365166697172</v>
       </c>
       <c r="D6" t="n">
-        <v>47.25544399621598</v>
+        <v>49.71079500453725</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.324238784308704</v>
+        <v>9.82140403328509</v>
       </c>
       <c r="C7" t="n">
-        <v>209.603134856694</v>
+        <v>142.0510388228795</v>
       </c>
       <c r="D7" t="n">
-        <v>33.59638818703009</v>
+        <v>34.31502750653876</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>119.8321247803657</v>
+        <v>86.36925428111314</v>
       </c>
       <c r="D8" t="n">
-        <v>30.45872252425729</v>
+        <v>32.21114217633784</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>35.94374694788421</v>
+        <v>32.9484347022272</v>
       </c>
       <c r="D9" t="n">
-        <v>30.84062238120929</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>23.20360698987336</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>18.8358114536793</v>
+        <v>20.7904711328347</v>
       </c>
       <c r="D11" t="n">
-        <v>22.7451308119901</v>
+        <v>23.27821981539612</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.75370449942107</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.29148125717007</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.46681318560274</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.90016483380309</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>11.98615772114931</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>9.919578803709772</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>30.22212132753381</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>6.138868394655306</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>30.49799243242716</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.060107594137308</v>
+        <v>4.771293842639499</v>
       </c>
       <c r="C2" t="n">
-        <v>6.258641614573417</v>
+        <v>8.229991004701011</v>
       </c>
       <c r="D2" t="n">
-        <v>13.29580915861455</v>
+        <v>12.29835349109979</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.48845269282518</v>
+        <v>16.27737693641212</v>
       </c>
       <c r="C3" t="n">
-        <v>25.11801501315465</v>
+        <v>17.0676838383308</v>
       </c>
       <c r="D3" t="n">
-        <v>56.46031047123407</v>
+        <v>69.42919764433444</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.5081130091059</v>
+        <v>45.74158903626739</v>
       </c>
       <c r="C4" t="n">
-        <v>130.9837969529052</v>
+        <v>70.60336789861363</v>
       </c>
       <c r="D4" t="n">
-        <v>127.7037778730166</v>
+        <v>146.8478581058294</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.97158004096841</v>
+        <v>56.89227946110267</v>
       </c>
       <c r="C5" t="n">
-        <v>279.798095710341</v>
+        <v>166.9461971071701</v>
       </c>
       <c r="D5" t="n">
-        <v>108.3604028562417</v>
+        <v>130.3024640461579</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.02902012943346</v>
+        <v>46.77242412572655</v>
       </c>
       <c r="C6" t="n">
-        <v>307.0798826636557</v>
+        <v>232.936332543528</v>
       </c>
       <c r="D6" t="n">
-        <v>59.4516957260741</v>
+        <v>67.94479511551327</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.78632315783946</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="C7" t="n">
-        <v>260.7462997617274</v>
+        <v>200.3805969229995</v>
       </c>
       <c r="D7" t="n">
-        <v>37.84833749412304</v>
+        <v>38.98618308334508</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.17381040138069</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>179.4978415059656</v>
+        <v>129.5121571442392</v>
       </c>
       <c r="D8" t="n">
-        <v>31.71045084717197</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>72.88593131098743</v>
+        <v>61.12655730951914</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>32.31422568528377</v>
       </c>
       <c r="D10" t="n">
-        <v>24.05772749256809</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>22.21204180858408</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.70640068316797</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.91359050649305</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.56913593102267</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>13.61684065790326</v>
+      </c>
+      <c r="D15" t="n">
         <v>12.541826921753</v>
-      </c>
-      <c r="D15" t="n">
-        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>7.852999886270235</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>34.94432778496098</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.184388641949153</v>
+        <v>3.095450511490193</v>
       </c>
       <c r="C2" t="n">
-        <v>3.947607518776425</v>
+        <v>4.059526757060561</v>
       </c>
       <c r="D2" t="n">
-        <v>9.969647936626359</v>
+        <v>9.653525175858887</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.17152811080271</v>
+        <v>16.48845269282518</v>
       </c>
       <c r="C3" t="n">
-        <v>25.22109852210056</v>
+        <v>24.31789063419349</v>
       </c>
       <c r="D3" t="n">
-        <v>54.59989857168636</v>
+        <v>64.6971737098648</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.51338160052563</v>
+        <v>41.14700978039232</v>
       </c>
       <c r="C4" t="n">
-        <v>107.4365782665454</v>
+        <v>60.08688649072178</v>
       </c>
       <c r="D4" t="n">
-        <v>128.6482191645021</v>
+        <v>148.3155709236784</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.12575548826417</v>
+        <v>63.17546476828226</v>
       </c>
       <c r="C5" t="n">
-        <v>272.9258617806133</v>
+        <v>158.2086425393735</v>
       </c>
       <c r="D5" t="n">
-        <v>119.2578023733813</v>
+        <v>146.3540390105933</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.02651685467723</v>
+        <v>55.30577517103983</v>
       </c>
       <c r="C6" t="n">
-        <v>362.4661611464437</v>
+        <v>255.6382664565313</v>
       </c>
       <c r="D6" t="n">
-        <v>68.99133816824036</v>
+        <v>81.02658327460202</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.75017841923158</v>
+        <v>20.4213339960379</v>
       </c>
       <c r="C7" t="n">
-        <v>320.8125695506599</v>
+        <v>251.2842153881966</v>
       </c>
       <c r="D7" t="n">
-        <v>42.27994663109313</v>
+        <v>43.83699849002857</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>5.340707511102648</v>
       </c>
       <c r="C8" t="n">
-        <v>222.3903987045087</v>
+        <v>167.1474553865407</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>35.88287859022092</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>76.87968097186344</v>
+        <v>73.1078062921472</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>25.90832191507333</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>21.67895280517806</v>
+        <v>24.52209415667683</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>18.00819813899924</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.6666888066416</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.44775906859456</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.98419422574081</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>7.525096153051802</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.373285111792041</v>
+        <v>5.220934291184538</v>
       </c>
       <c r="C2" t="n">
-        <v>15.86896989144544</v>
+        <v>13.20843361293659</v>
       </c>
       <c r="D2" t="n">
-        <v>9.51706224496858</v>
+        <v>12.78333685699772</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.05938788834032</v>
+        <v>13.55302705712722</v>
       </c>
       <c r="C3" t="n">
-        <v>20.75905520629881</v>
+        <v>20.07183181332604</v>
       </c>
       <c r="D3" t="n">
-        <v>50.65818153913542</v>
+        <v>58.96867585558466</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.57871672835365</v>
+        <v>36.29717612141307</v>
       </c>
       <c r="C4" t="n">
-        <v>88.71366779885453</v>
+        <v>60.21451369227387</v>
       </c>
       <c r="D4" t="n">
-        <v>126.5168448985822</v>
+        <v>145.2397553662731</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.39573610693204</v>
+        <v>63.27363953870694</v>
       </c>
       <c r="C5" t="n">
-        <v>242.4180518711437</v>
+        <v>136.8801736646116</v>
       </c>
       <c r="D5" t="n">
-        <v>131.603279754285</v>
+        <v>161.8901964302991</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.6064109527176</v>
+        <v>66.37498053642261</v>
       </c>
       <c r="C6" t="n">
-        <v>389.8775387967189</v>
+        <v>254.9137366507971</v>
       </c>
       <c r="D6" t="n">
-        <v>82.67690116544091</v>
+        <v>101.3134178351581</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.68568617038755</v>
+        <v>36.77037851486003</v>
       </c>
       <c r="C7" t="n">
-        <v>395.6109453895202</v>
+        <v>304.2239785920016</v>
       </c>
       <c r="D7" t="n">
-        <v>47.90928796724435</v>
+        <v>53.11942303368217</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.677267047210056</v>
+        <v>10.59796646734432</v>
       </c>
       <c r="C8" t="n">
-        <v>297.0768553050848</v>
+        <v>233.4056079461579</v>
       </c>
       <c r="D8" t="n">
-        <v>34.63115026730623</v>
+        <v>38.46978379091126</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>141.1124880176195</v>
+        <v>124.9156143929556</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>50.39310965898878</v>
+        <v>52.67076433284138</v>
       </c>
       <c r="D10" t="n">
-        <v>25.62361508084176</v>
+        <v>27.47420950334699</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>24.6997904911455</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.96750451476862</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>12.29148125717007</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>6.091744504851459</v>
+        <v>7.166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.03889435973815</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.141813637768045</v>
+        <v>5.085453107998478</v>
       </c>
       <c r="C2" t="n">
-        <v>14.16367412916873</v>
+        <v>6.702391576892974</v>
       </c>
       <c r="D2" t="n">
-        <v>13.57462550662065</v>
+        <v>6.180101798233672</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.491675673378405</v>
+        <v>3.691371367968007</v>
       </c>
       <c r="C2" t="n">
-        <v>9.520989235785567</v>
+        <v>7.397468951499716</v>
       </c>
       <c r="D2" t="n">
-        <v>7.156940763959247</v>
+        <v>9.408088249797183</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.90293015046658</v>
+        <v>18.33413837680919</v>
       </c>
       <c r="C3" t="n">
-        <v>35.05330178013237</v>
+        <v>32.80509953740717</v>
       </c>
       <c r="D3" t="n">
-        <v>54.6489859568987</v>
+        <v>64.4517367838031</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.70330087580177</v>
+        <v>48.97055723553515</v>
       </c>
       <c r="C4" t="n">
-        <v>130.6519662288698</v>
+        <v>84.99971623368884</v>
       </c>
       <c r="D4" t="n">
-        <v>128.8141345265198</v>
+        <v>149.0558086926805</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.011266555299</v>
+        <v>39.71169463678348</v>
       </c>
       <c r="C5" t="n">
-        <v>342.3108807782567</v>
+        <v>211.0021253352458</v>
       </c>
       <c r="D5" t="n">
-        <v>118.6687537508332</v>
+        <v>148.3666218042992</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.7912318963607</v>
+        <v>22.82268888062561</v>
       </c>
       <c r="C6" t="n">
-        <v>325.5151410540022</v>
+        <v>252.8206505453429</v>
       </c>
       <c r="D6" t="n">
-        <v>67.46177524502383</v>
+        <v>79.69827863075608</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>208.8844955371853</v>
+        <v>164.1491978977709</v>
       </c>
       <c r="D7" t="n">
-        <v>29.94330497952771</v>
+        <v>34.31502750653876</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.418625432636641</v>
+        <v>2.002765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>103.9768993567797</v>
+        <v>92.04375601165971</v>
       </c>
       <c r="D8" t="n">
-        <v>24.03318379996192</v>
+        <v>25.20146356801562</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>38.38437174064178</v>
+        <v>40.15937158992001</v>
       </c>
       <c r="D9" t="n">
-        <v>19.52499834206056</v>
+        <v>20.96718571959912</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.78359889890498</v>
+        <v>23.34596040698915</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>19.3600647277471</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.39340309196248</v>
+        <v>17.05884810899257</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>16.8811517745239</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>9.76348091873453</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>12.80100831567416</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>10.14636252339079</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>4.916592502868027</v>
+        <v>5.838453597155781</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.341509332357648</v>
+        <v>7.305184667300516</v>
       </c>
       <c r="C2" t="n">
-        <v>9.795878592974674</v>
+        <v>3.151410130632261</v>
       </c>
       <c r="D2" t="n">
-        <v>14.24614093632546</v>
+        <v>7.914849991637785</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.04742698944011</v>
+        <v>10.80413348523615</v>
       </c>
       <c r="C3" t="n">
-        <v>35.69143778789279</v>
+        <v>17.15604113171301</v>
       </c>
       <c r="D3" t="n">
-        <v>14.53968349989526</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
-        <v>18.43525839034661</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4585,10 +4585,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>20.72076704583318</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.60468413702056</v>
+        <v>39.2718716652809</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>50.67781649322036</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>26.15866757965626</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39618986264694</v>
+        <v>13.39891826488495</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13299398679868</v>
+        <v>70.14727797498593</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576022336781993</v>
+        <v>1.576343325280583</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.469316460358981</v>
+        <v>5.431028299893355</v>
       </c>
       <c r="C2" t="n">
-        <v>5.17381040138069</v>
+        <v>4.399211462729958</v>
       </c>
       <c r="D2" t="n">
-        <v>18.79850504091792</v>
+        <v>17.20316502151686</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.42035224833366</v>
+        <v>19.40915211295944</v>
       </c>
       <c r="C3" t="n">
-        <v>37.26223411468769</v>
+        <v>14.07335334037803</v>
       </c>
       <c r="D3" t="n">
-        <v>22.9925312334603</v>
+        <v>12.9590696960579</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>15.17487426454295</v>
+        <v>12.63509295365645</v>
       </c>
       <c r="C4" t="n">
-        <v>54.91798482786232</v>
+        <v>27.10801760966293</v>
       </c>
       <c r="D4" t="n">
-        <v>22.69211643596077</v>
+        <v>19.4376227963826</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.117048960983624</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
-        <v>16.58368222013712</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
-        <v>24.07441720354028</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.45180923259856</v>
+        <v>25.36836067773758</v>
       </c>
       <c r="D8" t="n">
-        <v>36.96770980341364</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.84843530511426</v>
       </c>
       <c r="D9" t="n">
-        <v>40.04843409934012</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43433440833059</v>
+        <v>15.44486258866365</v>
       </c>
       <c r="C21" t="n">
-        <v>86.10733933068646</v>
+        <v>86.16607549464983</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249333559648545</v>
+        <v>3.251550018666031</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.920920404312514</v>
+        <v>4.602433237509047</v>
       </c>
       <c r="C2" t="n">
-        <v>9.097855975255191</v>
+        <v>3.486186097780424</v>
       </c>
       <c r="D2" t="n">
-        <v>18.11029990024091</v>
+        <v>20.23578367993526</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.54659679155399</v>
+        <v>19.07535789351553</v>
       </c>
       <c r="C3" t="n">
-        <v>27.02260555939346</v>
+        <v>15.91903902436203</v>
       </c>
       <c r="D3" t="n">
-        <v>32.69219855141878</v>
+        <v>23.7141157960817</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.5629677073567</v>
+        <v>26.66132240423063</v>
       </c>
       <c r="C4" t="n">
-        <v>77.13788061808039</v>
+        <v>31.65154598491717</v>
       </c>
       <c r="D4" t="n">
-        <v>29.11176467403067</v>
+        <v>21.58175978245763</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.25359400733194</v>
+        <v>11.46190444708151</v>
       </c>
       <c r="C5" t="n">
-        <v>59.19938656608268</v>
+        <v>31.29320807286709</v>
       </c>
       <c r="D5" t="n">
-        <v>31.09685853201772</v>
+        <v>29.45243112740432</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.876741757621407</v>
       </c>
       <c r="C6" t="n">
-        <v>12.31700669748049</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.10573531908495</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.45733986592554</v>
+        <v>29.79113408536946</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.28749751309084</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>41.04687151455913</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>49.39663573917827</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.04418831335365</v>
+        <v>49.75497365122833</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5347,10 +5347,10 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5361,7 +5361,7 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.71842283758271</v>
+        <v>16.7429792367566</v>
       </c>
       <c r="C21" t="n">
-        <v>101.1464581673754</v>
+        <v>102.1321733442153</v>
       </c>
       <c r="D21" t="n">
-        <v>4.179605709395679</v>
+        <v>5.022893771026982</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.89481412692535</v>
+        <v>5.027529993447916</v>
       </c>
       <c r="C2" t="n">
-        <v>6.596362824834318</v>
+        <v>9.837111996553039</v>
       </c>
       <c r="D2" t="n">
-        <v>22.50852961526662</v>
+        <v>26.75655193154257</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.0521968592411</v>
+        <v>17.26403337918016</v>
       </c>
       <c r="C3" t="n">
-        <v>31.6859071545658</v>
+        <v>14.51513980728909</v>
       </c>
       <c r="D3" t="n">
-        <v>39.18155087649021</v>
+        <v>33.81629967278138</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.10649608261094</v>
+        <v>32.12376663065989</v>
       </c>
       <c r="C4" t="n">
-        <v>71.89240263428968</v>
+        <v>36.30993884156828</v>
       </c>
       <c r="D4" t="n">
-        <v>38.41578766717769</v>
+        <v>28.02693346083794</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.56256679672921</v>
+        <v>26.01631416254048</v>
       </c>
       <c r="C5" t="n">
-        <v>103.3044021793706</v>
+        <v>46.24031687002478</v>
       </c>
       <c r="D5" t="n">
-        <v>34.43480072645688</v>
+        <v>30.75324683553134</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.83398682699105</v>
+        <v>10.70694046251572</v>
       </c>
       <c r="C6" t="n">
-        <v>53.53470231257858</v>
+        <v>31.83905979642831</v>
       </c>
       <c r="D6" t="n">
-        <v>37.6755498981756</v>
+        <v>38.11831811279092</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.37951975538279</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.87734795689393</v>
       </c>
       <c r="D8" t="n">
-        <v>39.55461500410399</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.87187407682917</v>
       </c>
       <c r="C9" t="n">
-        <v>33.39218466454675</v>
+        <v>33.83593462686631</v>
       </c>
       <c r="D9" t="n">
-        <v>42.04530892977813</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
-        <v>48.82722207071512</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.28806265463436</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>47.51560713784138</v>
+        <v>47.29864089520282</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>45.26838664282043</v>
+        <v>45.78871292607123</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
         <v>45.7857676829585</v>
@@ -5633,7 +5633,7 @@
         <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.77765165941727</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.0291524772003</v>
+        <v>18.07659014101336</v>
       </c>
       <c r="C21" t="n">
-        <v>116.7602255666305</v>
+        <v>117.9282309199443</v>
       </c>
       <c r="D21" t="n">
-        <v>6.0097174924001</v>
+        <v>6.886320053719373</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.810383824360123</v>
+        <v>5.367214699117312</v>
       </c>
       <c r="C2" t="n">
-        <v>5.497787143782138</v>
+        <v>6.395104545463722</v>
       </c>
       <c r="D2" t="n">
-        <v>25.85236229593126</v>
+        <v>32.16696352964674</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.50732688338412</v>
+        <v>15.41834769519616</v>
       </c>
       <c r="C3" t="n">
-        <v>26.51700549170635</v>
+        <v>26.66426764734337</v>
       </c>
       <c r="D3" t="n">
-        <v>44.21300786075511</v>
+        <v>43.86448742574748</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.26567807941916</v>
+        <v>24.05772749256809</v>
       </c>
       <c r="C4" t="n">
-        <v>62.75429500316037</v>
+        <v>30.42632485001715</v>
       </c>
       <c r="D4" t="n">
-        <v>41.67028130675587</v>
+        <v>33.01715704152448</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.31650797586175</v>
+        <v>22.776546738526</v>
       </c>
       <c r="C5" t="n">
-        <v>88.18548753396975</v>
+        <v>42.55876297909924</v>
       </c>
       <c r="D5" t="n">
-        <v>32.54493639578177</v>
+        <v>27.58711048933538</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.16229147083699</v>
+        <v>12.63901994447344</v>
       </c>
       <c r="C6" t="n">
-        <v>73.45927197026759</v>
+        <v>36.70951015719674</v>
       </c>
       <c r="D6" t="n">
-        <v>30.67176177607885</v>
+        <v>30.30949687321178</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.689227946110266</v>
+        <v>5.449681506274044</v>
       </c>
       <c r="C7" t="n">
-        <v>31.4404702285041</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D7" t="n">
-        <v>31.08115056874977</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>29.45733986592554</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
-        <v>21.52187317249857</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>30.28593492830985</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.06830573313655</v>
+        <v>21.21065915025234</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.29539255245382</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.32797015314322</v>
       </c>
     </row>
     <row r="13">
@@ -5910,10 +5910,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
         <v>30.17892442854696</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
         <v>29.80684204863741</v>
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5969,10 +5969,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.039271564545139</v>
+        <v>7.068359426526651</v>
       </c>
       <c r="C21" t="n">
-        <v>65.99317091761068</v>
+        <v>67.14941455200318</v>
       </c>
       <c r="D21" t="n">
-        <v>4.399544727840712</v>
+        <v>5.301269569894989</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.583199194051611</v>
+        <v>5.364269456004572</v>
       </c>
       <c r="C2" t="n">
-        <v>5.7402788267311</v>
+        <v>4.323616889502953</v>
       </c>
       <c r="D2" t="n">
-        <v>19.52892533287755</v>
+        <v>27.67448603501334</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.03532722181966</v>
+        <v>17.63218876827272</v>
       </c>
       <c r="C3" t="n">
-        <v>23.34105166846792</v>
+        <v>25.83959957577605</v>
       </c>
       <c r="D3" t="n">
-        <v>55.24294331796801</v>
+        <v>61.14815575901258</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.22136056400782</v>
+        <v>28.28218786394211</v>
       </c>
       <c r="C4" t="n">
-        <v>64.46449950395831</v>
+        <v>53.39922112939251</v>
       </c>
       <c r="D4" t="n">
-        <v>55.1732392309665</v>
+        <v>49.12370987739765</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.71674224402496</v>
+        <v>30.99868376159304</v>
       </c>
       <c r="C5" t="n">
-        <v>105.0470043544087</v>
+        <v>51.32086123950202</v>
       </c>
       <c r="D5" t="n">
-        <v>40.37437433715008</v>
+        <v>33.96847056693964</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.50696703048563</v>
+        <v>23.18495378349268</v>
       </c>
       <c r="C6" t="n">
-        <v>112.1813649211703</v>
+        <v>55.58753676215866</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>32.4428346345401</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.19879606234337</v>
+        <v>11.13890945238431</v>
       </c>
       <c r="C7" t="n">
-        <v>74.13962312931062</v>
+        <v>40.78278138211675</v>
       </c>
       <c r="D7" t="n">
-        <v>33.41672835715293</v>
+        <v>33.53650157707104</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>31.96079651175491</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>31.29320807286708</v>
+        <v>31.87734795689393</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.05772749256809</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
         <v>34.82848155585983</v>
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.56448923440869</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.41280136633594</v>
       </c>
     </row>
     <row r="13">
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
         <v>29.80684204863741</v>
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6266,10 +6266,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.253772463093433</v>
+        <v>7.29549989217298</v>
       </c>
       <c r="C21" t="n">
-        <v>75.25788930459437</v>
+        <v>77.51468635433791</v>
       </c>
       <c r="D21" t="n">
-        <v>5.440329347320075</v>
+        <v>6.383562405651357</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.286310476741575</v>
+        <v>4.724169952835651</v>
       </c>
       <c r="C2" t="n">
-        <v>13.09062388842697</v>
+        <v>6.379396582195774</v>
       </c>
       <c r="D2" t="n">
-        <v>22.64499254615693</v>
+        <v>23.11328620108265</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.44489594093983</v>
+        <v>18.2359636063845</v>
       </c>
       <c r="C3" t="n">
-        <v>22.72255061479242</v>
+        <v>20.29763378530281</v>
       </c>
       <c r="D3" t="n">
-        <v>57.79548734900973</v>
+        <v>69.10031216341176</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.22434686484957</v>
+        <v>31.81746134693488</v>
       </c>
       <c r="C4" t="n">
-        <v>61.04409050236242</v>
+        <v>59.70400488606553</v>
       </c>
       <c r="D4" t="n">
-        <v>69.09736692029901</v>
+        <v>68.24226466990004</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.94517066394498</v>
+        <v>37.87091769132071</v>
       </c>
       <c r="C5" t="n">
-        <v>112.8518986031709</v>
+        <v>79.32521450314229</v>
       </c>
       <c r="D5" t="n">
-        <v>51.12451169865266</v>
+        <v>44.54680208019903</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.17365583712723</v>
+        <v>33.61013265488955</v>
       </c>
       <c r="C6" t="n">
-        <v>140.3977756889279</v>
+        <v>70.56115274733101</v>
       </c>
       <c r="D6" t="n">
-        <v>39.20511282139213</v>
+        <v>35.90447703971436</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.94224111636546</v>
+        <v>20.4213339960379</v>
       </c>
       <c r="C7" t="n">
-        <v>121.3302717770463</v>
+        <v>63.36003333668064</v>
       </c>
       <c r="D7" t="n">
-        <v>36.23139902522853</v>
+        <v>35.93196597543326</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.095892479846697</v>
+        <v>9.346238144429634</v>
       </c>
       <c r="C8" t="n">
-        <v>66.84229244364408</v>
+        <v>41.55738032076748</v>
       </c>
       <c r="D8" t="n">
-        <v>33.46287049925253</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>31.94999728700819</v>
+        <v>28.06718511671205</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.62008900065227</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>25.9436648324262</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,7 +6535,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
         <v>31.73990327829938</v>
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6619,10 +6619,10 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.454787903196511</v>
+        <v>7.511138405600343</v>
       </c>
       <c r="C21" t="n">
-        <v>83.86636391096074</v>
+        <v>87.31698396510397</v>
       </c>
       <c r="D21" t="n">
-        <v>6.522939415296947</v>
+        <v>7.511138405600343</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_59_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_59_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497625220732</v>
+        <v>10.84497635938983</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907166312434</v>
+        <v>37.78907203659937</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.882632243846888</v>
+        <v>6.022040417849935</v>
       </c>
       <c r="C2" t="n">
-        <v>9.451285148784043</v>
+        <v>6.763259934556276</v>
       </c>
       <c r="D2" t="n">
-        <v>20.70113209174824</v>
+        <v>21.58372327786612</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.11186248502191</v>
+        <v>16.30192062901829</v>
       </c>
       <c r="C3" t="n">
-        <v>22.85999529338698</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D3" t="n">
-        <v>71.29451828240336</v>
+        <v>80.94509821514953</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.88502201207866</v>
+        <v>35.27615850899639</v>
       </c>
       <c r="C4" t="n">
-        <v>54.7265440255342</v>
+        <v>42.58919715793088</v>
       </c>
       <c r="D4" t="n">
-        <v>86.48019177169304</v>
+        <v>118.5911956821977</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.04963683122264</v>
+        <v>45.0622196249286</v>
       </c>
       <c r="C5" t="n">
-        <v>95.30315838975913</v>
+        <v>80.40513697781378</v>
       </c>
       <c r="D5" t="n">
-        <v>57.72676500971247</v>
+        <v>87.54735152620933</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.23027840880406</v>
+        <v>42.62650357069227</v>
       </c>
       <c r="C6" t="n">
-        <v>100.0656165030604</v>
+        <v>102.8832324142488</v>
       </c>
       <c r="D6" t="n">
-        <v>41.82147045320988</v>
+        <v>54.21898046243861</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.48228446915921</v>
+        <v>28.80545939030566</v>
       </c>
       <c r="C7" t="n">
-        <v>84.08080038251383</v>
+        <v>94.92027678510286</v>
       </c>
       <c r="D7" t="n">
-        <v>38.08788393395925</v>
+        <v>40.8426679920758</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.02212253330794</v>
+        <v>14.85384276525424</v>
       </c>
       <c r="C8" t="n">
-        <v>63.50435024920493</v>
+        <v>62.92021036517807</v>
       </c>
       <c r="D8" t="n">
-        <v>36.38356991938679</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.765624340592267</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>40.82499653339935</v>
+        <v>38.162496759482</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>34.50155957034565</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
         <v>36.25005223160922</v>
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>28.20561154301086</v>
+        <v>27.98864530037232</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>26.27647730416588</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.713870808805265</v>
+        <v>7.68357681501636</v>
       </c>
       <c r="C21" t="n">
-        <v>96.42338511006581</v>
+        <v>93.16336888207336</v>
       </c>
       <c r="D21" t="n">
-        <v>8.678104659905923</v>
+        <v>7.68357681501636</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.370961763485052</v>
+        <v>7.919758730159019</v>
       </c>
       <c r="C2" t="n">
-        <v>7.268860002243384</v>
+        <v>10.41830663746715</v>
       </c>
       <c r="D2" t="n">
-        <v>25.02965771977243</v>
+        <v>28.74557278034661</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.42740440871263</v>
+        <v>18.17215000560846</v>
       </c>
       <c r="C3" t="n">
-        <v>30.18874190558942</v>
+        <v>20.52343575727957</v>
       </c>
       <c r="D3" t="n">
-        <v>71.0245376637355</v>
+        <v>79.17304360898402</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.04268248183489</v>
+        <v>32.8895298399724</v>
       </c>
       <c r="C4" t="n">
-        <v>55.93900244027901</v>
+        <v>39.05392367493812</v>
       </c>
       <c r="D4" t="n">
-        <v>100.9275909873891</v>
+        <v>128.8396599668302</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.17297718905925</v>
+        <v>48.67014243803564</v>
       </c>
       <c r="C5" t="n">
-        <v>97.16847902782808</v>
+        <v>78.6625348027757</v>
       </c>
       <c r="D5" t="n">
-        <v>73.11566027378122</v>
+        <v>107.7958979262998</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.4353248102714</v>
+        <v>51.72337779824321</v>
       </c>
       <c r="C6" t="n">
-        <v>125.4644113596297</v>
+        <v>115.2002391117292</v>
       </c>
       <c r="D6" t="n">
-        <v>49.87180162803373</v>
+        <v>66.65674212754145</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.60312155223958</v>
+        <v>38.98618308334508</v>
       </c>
       <c r="C7" t="n">
-        <v>113.0659196026967</v>
+        <v>120.1325395778652</v>
       </c>
       <c r="D7" t="n">
-        <v>41.44153409166636</v>
+        <v>46.65166915810418</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24.36697801940583</v>
+        <v>22.44766125760332</v>
       </c>
       <c r="C8" t="n">
-        <v>87.62098260402782</v>
+        <v>93.46238144429634</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.6484365108884</v>
+        <v>11.09374905798895</v>
       </c>
       <c r="C9" t="n">
-        <v>59.12968247908112</v>
+        <v>56.91093266748334</v>
       </c>
       <c r="D9" t="n">
-        <v>35.72187196672443</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>40.00131020953629</v>
+        <v>37.86600895279948</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1237,7 +1237,7 @@
         <v>30.8092064546734</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.87810872041993</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
         <v>33.30088212805181</v>
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1321,7 +1321,7 @@
         <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.902516349917921</v>
+        <v>7.867998190106801</v>
       </c>
       <c r="C21" t="n">
-        <v>105.6961561801522</v>
+        <v>101.3004766976251</v>
       </c>
       <c r="D21" t="n">
-        <v>9.8781454373974</v>
+        <v>8.851497963870152</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.963356539773379</v>
+        <v>9.359000864584843</v>
       </c>
       <c r="C2" t="n">
-        <v>7.162831250184728</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D2" t="n">
-        <v>30.34582153826891</v>
+        <v>28.57867567062465</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.21065915025234</v>
+        <v>21.79479903427919</v>
       </c>
       <c r="C3" t="n">
-        <v>29.31498644880976</v>
+        <v>30.0267535343887</v>
       </c>
       <c r="D3" t="n">
-        <v>73.29237486054562</v>
+        <v>82.24100518475531</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.77015753068178</v>
+        <v>33.06820792214531</v>
       </c>
       <c r="C4" t="n">
-        <v>64.41344862333747</v>
+        <v>44.69504598354029</v>
       </c>
       <c r="D4" t="n">
-        <v>109.7466306146382</v>
+        <v>136.7397837429043</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.03200643027521</v>
+        <v>48.79286090106649</v>
       </c>
       <c r="C5" t="n">
-        <v>98.78836273983532</v>
+        <v>74.71100029318228</v>
       </c>
       <c r="D5" t="n">
-        <v>89.46175954949061</v>
+        <v>123.6265796572796</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.27181491201868</v>
+        <v>58.32464936159877</v>
       </c>
       <c r="C6" t="n">
-        <v>138.9084644215855</v>
+        <v>118.8228881404</v>
       </c>
       <c r="D6" t="n">
-        <v>58.80766923208819</v>
+        <v>81.63035811271381</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>49.34656660626167</v>
+        <v>48.62792728675301</v>
       </c>
       <c r="C7" t="n">
-        <v>142.8894513623063</v>
+        <v>141.6318325531661</v>
       </c>
       <c r="D7" t="n">
-        <v>45.8132566186774</v>
+        <v>52.87987659384594</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>33.37942194439155</v>
+        <v>30.95941385342316</v>
       </c>
       <c r="C8" t="n">
-        <v>116.3272854762046</v>
+        <v>122.1686843164731</v>
       </c>
       <c r="D8" t="n">
-        <v>39.97185777840888</v>
+        <v>41.64082887562846</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.19531103988288</v>
+        <v>15.97499864350409</v>
       </c>
       <c r="C9" t="n">
-        <v>80.98436812331937</v>
+        <v>83.20311793491715</v>
       </c>
       <c r="D9" t="n">
-        <v>37.38593432542277</v>
+        <v>37.16405934426299</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.541205026947251</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>53.24017800130454</v>
+        <v>50.53546307610457</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>39.27088991757665</v>
+        <v>37.13853390395258</v>
       </c>
       <c r="D11" t="n">
-        <v>37.49392657288993</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1559,7 +1559,7 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>31.47974013667398</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
         <v>33.82120841130262</v>
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1632,7 +1632,7 @@
         <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>19.25796296650543</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.075947208229536</v>
+        <v>8.038072354452506</v>
       </c>
       <c r="C21" t="n">
-        <v>114.0727543162422</v>
+        <v>109.5187358294154</v>
       </c>
       <c r="D21" t="n">
-        <v>11.10442741131561</v>
+        <v>10.04759044306563</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.047385931711105</v>
+        <v>8.388052385084748</v>
       </c>
       <c r="C2" t="n">
-        <v>4.75558587937155</v>
+        <v>10.64312686173967</v>
       </c>
       <c r="D2" t="n">
-        <v>24.59670698219958</v>
+        <v>23.26545709524092</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.79894700927443</v>
+        <v>24.94620916491145</v>
       </c>
       <c r="C3" t="n">
-        <v>42.76002125846983</v>
+        <v>45.7248993252952</v>
       </c>
       <c r="D3" t="n">
-        <v>81.3181623427633</v>
+        <v>92.58371724899546</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.07499804061703</v>
+        <v>23.43235420496287</v>
       </c>
       <c r="C4" t="n">
-        <v>85.79100488331179</v>
+        <v>62.60114236129786</v>
       </c>
       <c r="D4" t="n">
-        <v>104.3990508696058</v>
+        <v>134.3914432343459</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.68590715456581</v>
+        <v>32.83946070705581</v>
       </c>
       <c r="C5" t="n">
-        <v>82.98222470146166</v>
+        <v>70.98035901704441</v>
       </c>
       <c r="D5" t="n">
-        <v>60.03387211469246</v>
+        <v>83.17857424231102</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.63151012020474</v>
+        <v>30.18874190558942</v>
       </c>
       <c r="C6" t="n">
-        <v>94.10837143369076</v>
+        <v>93.26308666033425</v>
       </c>
       <c r="D6" t="n">
-        <v>30.14849024971531</v>
+        <v>34.81768233111314</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.09815907489146</v>
+        <v>20.48122060599696</v>
       </c>
       <c r="C7" t="n">
-        <v>81.80510920406972</v>
+        <v>85.87739868128548</v>
       </c>
       <c r="D7" t="n">
-        <v>28.086820070797</v>
+        <v>29.2845522699781</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.93314334511998</v>
+        <v>11.09865779651019</v>
       </c>
       <c r="C8" t="n">
-        <v>59.6657167255999</v>
+        <v>61.33468782281948</v>
       </c>
       <c r="D8" t="n">
-        <v>27.53802310412303</v>
+        <v>27.37112599440107</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>40.60312155223957</v>
+        <v>38.49530923122167</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>29.04009709162065</v>
       </c>
       <c r="D10" t="n">
-        <v>29.32480392585223</v>
+        <v>28.89774367450487</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>28.25371718051895</v>
+        <v>28.07602084605028</v>
       </c>
     </row>
     <row r="12">
@@ -1856,7 +1856,7 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
         <v>27.55471281509523</v>
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
         <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>23.96838845148163</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1929,7 +1929,7 @@
         <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>16.58662746324986</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
-        <v>9.628981483252716</v>
+        <v>9.027170140549421</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.844924920458009</v>
+        <v>5.091343594223958</v>
       </c>
       <c r="C2" t="n">
-        <v>2.821542902005333</v>
+        <v>4.290237467558561</v>
       </c>
       <c r="D2" t="n">
-        <v>17.03135917327366</v>
+        <v>16.11047982669016</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.03733177495716</v>
+        <v>27.56747553525044</v>
       </c>
       <c r="C3" t="n">
-        <v>30.60598467989431</v>
+        <v>44.52225838759285</v>
       </c>
       <c r="D3" t="n">
-        <v>83.28165775125693</v>
+        <v>90.47786842338604</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.31895449735575</v>
+        <v>34.11475097487241</v>
       </c>
       <c r="C4" t="n">
-        <v>99.48540360985054</v>
+        <v>89.5687700492535</v>
       </c>
       <c r="D4" t="n">
-        <v>119.6632641752352</v>
+        <v>149.208961334543</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.70478134512475</v>
+        <v>36.05468443846411</v>
       </c>
       <c r="C5" t="n">
-        <v>119.8713946885356</v>
+        <v>93.7569057555704</v>
       </c>
       <c r="D5" t="n">
-        <v>76.91993262773761</v>
+        <v>104.1143440353743</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.87051678069322</v>
+        <v>36.22649028670731</v>
       </c>
       <c r="C6" t="n">
-        <v>113.7914311561351</v>
+        <v>107.1499079369054</v>
       </c>
       <c r="D6" t="n">
-        <v>37.19253002768617</v>
+        <v>45.16235789076178</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.9603134856694</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="C7" t="n">
-        <v>105.5202067478557</v>
+        <v>107.0772586067911</v>
       </c>
       <c r="D7" t="n">
-        <v>30.42239785920016</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.930378028456486</v>
+        <v>9.346238144429634</v>
       </c>
       <c r="C8" t="n">
-        <v>77.4402589109884</v>
+        <v>80.77820110542756</v>
       </c>
       <c r="D8" t="n">
-        <v>28.78975142703771</v>
+        <v>28.53940576245478</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>47.59218345877262</v>
+        <v>44.26405874137593</v>
       </c>
       <c r="D9" t="n">
-        <v>28.95468504135117</v>
+        <v>28.28906009787183</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>32.02951885105219</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>30.38607319414302</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2164,7 +2164,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
         <v>21.47965802121596</v>
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2226,7 +2226,7 @@
         <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
-        <v>8.025787482217675</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.283766144256333</v>
+        <v>4.499349728563132</v>
       </c>
       <c r="C2" t="n">
-        <v>6.400995031689204</v>
+        <v>5.329908286355933</v>
       </c>
       <c r="D2" t="n">
-        <v>16.8350096324243</v>
+        <v>20.23480193223101</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.65735435568464</v>
+        <v>22.58019719767664</v>
       </c>
       <c r="C3" t="n">
-        <v>19.90002596508285</v>
+        <v>29.6095107600838</v>
       </c>
       <c r="D3" t="n">
-        <v>77.81823177712343</v>
+        <v>82.82023633026093</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.29114676646735</v>
+        <v>43.08694324398402</v>
       </c>
       <c r="C4" t="n">
-        <v>87.28424314147117</v>
+        <v>100.7744383455266</v>
       </c>
       <c r="D4" t="n">
-        <v>132.7578150544792</v>
+        <v>159.5340019401067</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.68148144213009</v>
+        <v>43.34416114249668</v>
       </c>
       <c r="C5" t="n">
-        <v>153.4962535589888</v>
+        <v>129.4679784975481</v>
       </c>
       <c r="D5" t="n">
-        <v>99.57376090323277</v>
+        <v>130.7687942056752</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.94222542083224</v>
+        <v>42.62650357069227</v>
       </c>
       <c r="C6" t="n">
-        <v>150.7827029044506</v>
+        <v>128.6040405178109</v>
       </c>
       <c r="D6" t="n">
-        <v>50.35482149852316</v>
+        <v>63.83912621635311</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.78171751895449</v>
+        <v>28.86534600026472</v>
       </c>
       <c r="C7" t="n">
-        <v>135.2239652875472</v>
+        <v>131.1516758103314</v>
       </c>
       <c r="D7" t="n">
-        <v>33.71616140694821</v>
+        <v>37.00992495469625</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.85384276525424</v>
+        <v>13.85246010692249</v>
       </c>
       <c r="C8" t="n">
-        <v>107.4817386609408</v>
+        <v>109.6514010873262</v>
       </c>
       <c r="D8" t="n">
-        <v>30.62561963397925</v>
+        <v>30.70906818884022</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.767186925373262</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>70.11249404649018</v>
+        <v>68.78124415953151</v>
       </c>
       <c r="D9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.06562253193106</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>43.2754388031994</v>
+        <v>41.28249096357838</v>
       </c>
       <c r="D10" t="n">
-        <v>30.89069151412589</v>
+        <v>30.46363126277853</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>34.82848155585983</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2475,7 +2475,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
         <v>26.03594911662541</v>
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.77239876353076</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>20.28094407433061</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>15.11106066376691</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>6.955682484588652</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>34.9050578767911</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.100359250011427</v>
+        <v>2.651700549170635</v>
       </c>
       <c r="C2" t="n">
-        <v>2.894192232119597</v>
+        <v>2.453387512912779</v>
       </c>
       <c r="D2" t="n">
-        <v>11.59444038715483</v>
+        <v>14.005612748785</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.02060100625596</v>
+        <v>21.94206118991621</v>
       </c>
       <c r="C3" t="n">
-        <v>23.48831382410494</v>
+        <v>27.64110661306895</v>
       </c>
       <c r="D3" t="n">
-        <v>76.6597694861122</v>
+        <v>82.88404993103697</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.97506506342888</v>
+        <v>47.66875977970388</v>
       </c>
       <c r="C4" t="n">
-        <v>81.55378179178254</v>
+        <v>100.3532685804047</v>
       </c>
       <c r="D4" t="n">
-        <v>141.7682954840564</v>
+        <v>168.3402788472006</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.93950116189775</v>
+        <v>45.62672455487052</v>
       </c>
       <c r="C5" t="n">
-        <v>179.3162181806799</v>
+        <v>163.4609927570939</v>
       </c>
       <c r="D5" t="n">
-        <v>108.3849465488479</v>
+        <v>140.2426595516569</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.54850353370026</v>
+        <v>35.62271544859552</v>
       </c>
       <c r="C6" t="n">
-        <v>186.365166697172</v>
+        <v>158.7122791116522</v>
       </c>
       <c r="D6" t="n">
-        <v>49.71079500453725</v>
+        <v>61.50453017565419</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.82140403328509</v>
+        <v>9.162651323735481</v>
       </c>
       <c r="C7" t="n">
-        <v>142.0510388228795</v>
+        <v>141.0928530635346</v>
       </c>
       <c r="D7" t="n">
-        <v>34.31502750653876</v>
+        <v>36.83026512481909</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.673119072214817</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>86.36925428111314</v>
+        <v>85.03407740333748</v>
       </c>
       <c r="D8" t="n">
-        <v>32.21114217633784</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>32.9484347022272</v>
+        <v>31.50624732468863</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.48831382410494</v>
       </c>
     </row>
     <row r="11">
@@ -2772,7 +2772,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
         <v>20.7904711328347</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.05550195525234</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>12.81278928812512</v>
       </c>
       <c r="D16" t="n">
-        <v>9.919578803709772</v>
+        <v>9.506263020221864</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.66664774891259</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>29.96293993361265</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.771293842639499</v>
+        <v>3.353650157707104</v>
       </c>
       <c r="C2" t="n">
-        <v>8.229991004701011</v>
+        <v>2.484803439448677</v>
       </c>
       <c r="D2" t="n">
-        <v>12.29835349109979</v>
+        <v>17.48394486493144</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.27737693641212</v>
+        <v>15.66869335977909</v>
       </c>
       <c r="C3" t="n">
-        <v>17.0676838383308</v>
+        <v>18.27032477603314</v>
       </c>
       <c r="D3" t="n">
-        <v>69.42919764433444</v>
+        <v>75.56512079587699</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.74158903626739</v>
+        <v>45.42252103238718</v>
       </c>
       <c r="C4" t="n">
-        <v>70.60336789861363</v>
+        <v>85.54851320036282</v>
       </c>
       <c r="D4" t="n">
-        <v>146.8478581058294</v>
+        <v>170.9183483185527</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.89227946110267</v>
+        <v>56.76956099807182</v>
       </c>
       <c r="C5" t="n">
-        <v>166.9461971071701</v>
+        <v>173.3766445699867</v>
       </c>
       <c r="D5" t="n">
-        <v>130.3024640461579</v>
+        <v>165.4981192434061</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.77242412572655</v>
+        <v>45.80638438474769</v>
       </c>
       <c r="C6" t="n">
-        <v>232.936332543528</v>
+        <v>207.5375376869588</v>
       </c>
       <c r="D6" t="n">
-        <v>67.94479511551327</v>
+        <v>83.32092765942681</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.02020009562846</v>
+        <v>20.30156077611979</v>
       </c>
       <c r="C7" t="n">
-        <v>200.3805969229995</v>
+        <v>180.5581290265521</v>
       </c>
       <c r="D7" t="n">
-        <v>38.98618308334508</v>
+        <v>43.77711188006952</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.508987279156353</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>129.5121571442392</v>
+        <v>129.0114658150733</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>61.12655730951914</v>
+        <v>58.46405753560178</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31422568528377</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>24.87748682561417</v>
+        <v>24.52209415667683</v>
       </c>
       <c r="D11" t="n">
         <v>23.98900515327081</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.65909686691488</v>
+        <v>18.00819813899924</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>15.60978849752428</v>
+      </c>
+      <c r="D13" t="n">
         <v>15.86995163914969</v>
-      </c>
-      <c r="D13" t="n">
-        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>8.266315669758143</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.095450511490193</v>
+        <v>2.581996462169111</v>
       </c>
       <c r="C2" t="n">
-        <v>4.059526757060561</v>
+        <v>1.604175748739288</v>
       </c>
       <c r="D2" t="n">
-        <v>9.653525175858887</v>
+        <v>13.38416645199677</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.48845269282518</v>
+        <v>14.03899217072939</v>
       </c>
       <c r="C3" t="n">
-        <v>24.31789063419349</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D3" t="n">
-        <v>64.6971737098648</v>
+        <v>72.87513208624073</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.14700978039232</v>
+        <v>40.54716193309751</v>
       </c>
       <c r="C4" t="n">
-        <v>60.08688649072178</v>
+        <v>70.52679157768236</v>
       </c>
       <c r="D4" t="n">
-        <v>148.3155709236784</v>
+        <v>170.7907211170006</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>63.17546476828226</v>
+        <v>62.73367830137119</v>
       </c>
       <c r="C5" t="n">
-        <v>158.2086425393735</v>
+        <v>171.5113239319178</v>
       </c>
       <c r="D5" t="n">
-        <v>146.3540390105933</v>
+        <v>182.4332671416635</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.30577517103983</v>
+        <v>53.93721887131977</v>
       </c>
       <c r="C6" t="n">
-        <v>255.6382664565313</v>
+        <v>240.5841471596107</v>
       </c>
       <c r="D6" t="n">
-        <v>81.02658327460202</v>
+        <v>100.1863714706828</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.4213339960379</v>
+        <v>19.04394196697963</v>
       </c>
       <c r="C7" t="n">
-        <v>251.2842153881966</v>
+        <v>225.5329731058027</v>
       </c>
       <c r="D7" t="n">
-        <v>43.83699849002857</v>
+        <v>50.18497914568845</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>167.1474553865407</v>
+        <v>163.7260646372405</v>
       </c>
       <c r="D8" t="n">
-        <v>35.88287859022092</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>73.1078062921472</v>
+        <v>68.33749419721195</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>32.59893251951534</v>
       </c>
       <c r="D10" t="n">
-        <v>25.90832191507333</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.52209415667683</v>
+        <v>23.98900515327081</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>7.525096153051802</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.220934291184538</v>
+        <v>3.829797794266807</v>
       </c>
       <c r="C2" t="n">
-        <v>13.20843361293659</v>
+        <v>7.178539213452678</v>
       </c>
       <c r="D2" t="n">
-        <v>12.78333685699772</v>
+        <v>20.64517247260617</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.55302705712722</v>
+        <v>11.45699570856028</v>
       </c>
       <c r="C3" t="n">
-        <v>20.07183181332604</v>
+        <v>10.57833151325938</v>
       </c>
       <c r="D3" t="n">
-        <v>58.96867585558466</v>
+        <v>67.49515466696822</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.29717612141307</v>
+        <v>34.30619177720055</v>
       </c>
       <c r="C4" t="n">
-        <v>60.21451369227387</v>
+        <v>54.95627298832795</v>
       </c>
       <c r="D4" t="n">
-        <v>145.2397553662731</v>
+        <v>168.2892279665797</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>63.27363953870694</v>
+        <v>61.99736752318609</v>
       </c>
       <c r="C5" t="n">
-        <v>136.8801736646116</v>
+        <v>153.1280981698963</v>
       </c>
       <c r="D5" t="n">
-        <v>161.8901964302991</v>
+        <v>194.7542008299611</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>66.37498053642261</v>
+        <v>65.77120569831082</v>
       </c>
       <c r="C6" t="n">
-        <v>254.9137366507971</v>
+        <v>254.5112200920559</v>
       </c>
       <c r="D6" t="n">
-        <v>101.3134178351581</v>
+        <v>125.6254179831261</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.77037851486003</v>
+        <v>34.49468733641593</v>
       </c>
       <c r="C7" t="n">
-        <v>304.2239785920016</v>
+        <v>276.0173853012865</v>
       </c>
       <c r="D7" t="n">
-        <v>53.11942303368217</v>
+        <v>62.22218774745859</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.59796646734432</v>
+        <v>9.846929473595507</v>
       </c>
       <c r="C8" t="n">
-        <v>233.4056079461579</v>
+        <v>219.8034935038184</v>
       </c>
       <c r="D8" t="n">
-        <v>38.46978379091126</v>
+        <v>38.88702656521616</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.995312245657018</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>124.9156143929556</v>
+        <v>118.7031149204818</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>33.9468721174462</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>52.67076433284138</v>
+        <v>49.53898915629405</v>
       </c>
       <c r="D10" t="n">
-        <v>27.47420950334699</v>
+        <v>26.76244241776806</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>24.6997904911455</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>12.29148125717007</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.085453107998478</v>
+        <v>5.391758391723482</v>
       </c>
       <c r="C2" t="n">
-        <v>6.702391576892974</v>
+        <v>5.561600744558181</v>
       </c>
       <c r="D2" t="n">
-        <v>6.180101798233672</v>
+        <v>13.15051049838602</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.691371367968007</v>
+        <v>2.71158715912969</v>
       </c>
       <c r="C2" t="n">
-        <v>7.397468951499716</v>
+        <v>4.077198215737003</v>
       </c>
       <c r="D2" t="n">
-        <v>9.408088249797183</v>
+        <v>15.19450921862788</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.33413837680919</v>
+        <v>15.75705065316131</v>
       </c>
       <c r="C3" t="n">
-        <v>32.80509953740717</v>
+        <v>17.36220814960484</v>
       </c>
       <c r="D3" t="n">
-        <v>64.4517367838031</v>
+        <v>75.74674412116266</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.97055723553515</v>
+        <v>47.29864089520283</v>
       </c>
       <c r="C4" t="n">
-        <v>84.99971623368884</v>
+        <v>80.11159441424397</v>
       </c>
       <c r="D4" t="n">
-        <v>149.0558086926805</v>
+        <v>173.572994110836</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.71169463678348</v>
+        <v>38.75449062514284</v>
       </c>
       <c r="C5" t="n">
-        <v>211.0021253352458</v>
+        <v>220.107835292135</v>
       </c>
       <c r="D5" t="n">
-        <v>148.3666218042992</v>
+        <v>179.610742491954</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.82268888062561</v>
+        <v>21.41388092503143</v>
       </c>
       <c r="C6" t="n">
-        <v>252.8206505453429</v>
+        <v>234.1841338756257</v>
       </c>
       <c r="D6" t="n">
-        <v>79.69827863075608</v>
+        <v>97.20774893599796</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.006733365209485</v>
+        <v>6.527640485537042</v>
       </c>
       <c r="C7" t="n">
-        <v>164.1491978977709</v>
+        <v>154.567340304322</v>
       </c>
       <c r="D7" t="n">
-        <v>34.31502750653876</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.002765316663493</v>
+        <v>1.752419652080557</v>
       </c>
       <c r="C8" t="n">
-        <v>92.04375601165971</v>
+        <v>87.45408549430587</v>
       </c>
       <c r="D8" t="n">
-        <v>25.20146356801562</v>
+        <v>24.95111790343269</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>40.15937158992001</v>
+        <v>37.82968428774233</v>
       </c>
       <c r="D9" t="n">
-        <v>20.96718571959912</v>
+        <v>20.41249826669968</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>23.34596040698915</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D10" t="n">
-        <v>19.3600647277471</v>
+        <v>19.07535789351553</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>17.05884810899257</v>
+        <v>16.34806277111788</v>
       </c>
       <c r="D11" t="n">
-        <v>16.8811517745239</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.28224461720434</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>10.14636252339079</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.838453597155781</v>
+        <v>5.223879534297279</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.305184667300516</v>
+        <v>6.413757751844412</v>
       </c>
       <c r="C2" t="n">
-        <v>3.151410130632261</v>
+        <v>6.027930904075415</v>
       </c>
       <c r="D2" t="n">
-        <v>7.914849991637785</v>
+        <v>28.75833550050182</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.80413348523615</v>
+        <v>11.45699570856028</v>
       </c>
       <c r="C3" t="n">
-        <v>17.15604113171301</v>
+        <v>14.01444847812322</v>
       </c>
       <c r="D3" t="n">
-        <v>8.325220532012953</v>
+        <v>14.18134558784518</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39891826488495</v>
+        <v>13.39786395711344</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14727797498593</v>
+        <v>70.14175836371153</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576343325280583</v>
+        <v>1.576219289072169</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.431028299893355</v>
+        <v>5.355433726666351</v>
       </c>
       <c r="C2" t="n">
-        <v>4.399211462729958</v>
+        <v>4.236241343824987</v>
       </c>
       <c r="D2" t="n">
-        <v>17.20316502151686</v>
+        <v>23.29196428325557</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.40915211295944</v>
+        <v>17.86289947877071</v>
       </c>
       <c r="C3" t="n">
-        <v>14.07335334037803</v>
+        <v>19.95402208881642</v>
       </c>
       <c r="D3" t="n">
-        <v>12.9590696960579</v>
+        <v>34.91094836301658</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.63509295365645</v>
+        <v>13.37533072265855</v>
       </c>
       <c r="C4" t="n">
-        <v>27.10801760966293</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D4" t="n">
-        <v>19.4376227963826</v>
+        <v>22.50067563363265</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.473243451175969</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4910,10 +4910,10 @@
         <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.36836067773758</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.84843530511426</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44486258866365</v>
+        <v>15.43870843234517</v>
       </c>
       <c r="C21" t="n">
-        <v>86.16607549464983</v>
+        <v>86.13174178045205</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251550018666031</v>
+        <v>3.250254406809511</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.602433237509047</v>
+        <v>5.433973543006096</v>
       </c>
       <c r="C2" t="n">
-        <v>3.486186097780424</v>
+        <v>6.947828502954677</v>
       </c>
       <c r="D2" t="n">
-        <v>20.23578367993526</v>
+        <v>32.79233681725196</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.07535789351553</v>
+        <v>18.25559856046944</v>
       </c>
       <c r="C3" t="n">
-        <v>15.91903902436203</v>
+        <v>17.84817326320701</v>
       </c>
       <c r="D3" t="n">
-        <v>23.7141157960817</v>
+        <v>45.44510122958485</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.66132240423063</v>
+        <v>25.4233385491754</v>
       </c>
       <c r="C4" t="n">
-        <v>31.65154598491717</v>
+        <v>38.4285503873329</v>
       </c>
       <c r="D4" t="n">
-        <v>21.58175978245763</v>
+        <v>34.91880234465055</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.46190444708151</v>
+        <v>11.83005983617407</v>
       </c>
       <c r="C5" t="n">
-        <v>31.29320807286709</v>
+        <v>25.40272184738622</v>
       </c>
       <c r="D5" t="n">
-        <v>29.45243112740432</v>
+        <v>30.75324683553134</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.13430381349934</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.79113408536946</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5249,7 +5249,7 @@
         <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5336,7 +5336,7 @@
         <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5361,7 +5361,7 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.7429792367566</v>
+        <v>16.73060901068245</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1321733442153</v>
+        <v>102.056714965163</v>
       </c>
       <c r="D21" t="n">
-        <v>5.022893771026982</v>
+        <v>4.182652252670612</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.027529993447916</v>
+        <v>5.313218575383737</v>
       </c>
       <c r="C2" t="n">
-        <v>9.837111996553039</v>
+        <v>4.092906179004952</v>
       </c>
       <c r="D2" t="n">
-        <v>26.75655193154257</v>
+        <v>35.26241404113694</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.26403337918016</v>
+        <v>18.61393647251952</v>
       </c>
       <c r="C3" t="n">
-        <v>14.51513980728909</v>
+        <v>23.10052348092745</v>
       </c>
       <c r="D3" t="n">
-        <v>33.81629967278138</v>
+        <v>60.25967408666923</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.12376663065989</v>
+        <v>30.51566389110361</v>
       </c>
       <c r="C4" t="n">
-        <v>36.30993884156828</v>
+        <v>41.91277298970483</v>
       </c>
       <c r="D4" t="n">
-        <v>28.02693346083794</v>
+        <v>49.03437083631119</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.01631416254048</v>
+        <v>24.86276061005048</v>
       </c>
       <c r="C5" t="n">
-        <v>46.24031687002478</v>
+        <v>49.99550183876883</v>
       </c>
       <c r="D5" t="n">
-        <v>30.75324683553134</v>
+        <v>35.80924751240241</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.70694046251572</v>
+        <v>11.06920536538279</v>
       </c>
       <c r="C6" t="n">
-        <v>31.83905979642831</v>
+        <v>26.64659618866693</v>
       </c>
       <c r="D6" t="n">
-        <v>38.11831811279092</v>
+        <v>38.44033135978387</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.13997331554657</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>31.62700229231099</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>33.83593462686631</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>8.707120388964958</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5619,7 +5619,7 @@
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07659014101336</v>
+        <v>18.05319600065912</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9282309199443</v>
+        <v>117.7756120043</v>
       </c>
       <c r="D21" t="n">
-        <v>6.886320053719373</v>
+        <v>6.017732000219707</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.367214699117312</v>
+        <v>6.235079669671493</v>
       </c>
       <c r="C2" t="n">
-        <v>6.395104545463722</v>
+        <v>5.228788272818512</v>
       </c>
       <c r="D2" t="n">
-        <v>32.16696352964674</v>
+        <v>30.13769102496859</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.41834769519616</v>
+        <v>16.35591675275186</v>
       </c>
       <c r="C3" t="n">
-        <v>26.66426764734337</v>
+        <v>17.81872083207961</v>
       </c>
       <c r="D3" t="n">
-        <v>43.86448742574748</v>
+        <v>69.29175296573987</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.05772749256809</v>
+        <v>24.47889725768997</v>
       </c>
       <c r="C4" t="n">
-        <v>30.42632485001715</v>
+        <v>42.52538355715484</v>
       </c>
       <c r="D4" t="n">
-        <v>33.01715704152448</v>
+        <v>58.6191736728728</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.776546738526</v>
+        <v>21.50027472300515</v>
       </c>
       <c r="C5" t="n">
-        <v>42.55876297909924</v>
+        <v>47.73748211900116</v>
       </c>
       <c r="D5" t="n">
-        <v>27.58711048933538</v>
+        <v>36.00559705325178</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.63901994447344</v>
+        <v>12.15600007398401</v>
       </c>
       <c r="C6" t="n">
         <v>36.70951015719674</v>
       </c>
       <c r="D6" t="n">
-        <v>30.30949687321178</v>
+        <v>31.87931145230244</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.449681506274044</v>
+        <v>5.509568116233099</v>
       </c>
       <c r="C7" t="n">
-        <v>21.85861263505523</v>
+        <v>19.28348840681585</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>30.78171751895449</v>
       </c>
     </row>
     <row r="8">
@@ -5843,7 +5843,7 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D8" t="n">
         <v>30.0414797499524</v>
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
         <v>34.29539255245382</v>
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5916,7 +5916,7 @@
         <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -5972,7 +5972,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.068359426526651</v>
+        <v>7.054583504702939</v>
       </c>
       <c r="C21" t="n">
-        <v>67.14941455200318</v>
+        <v>66.13672035659006</v>
       </c>
       <c r="D21" t="n">
-        <v>5.301269569894989</v>
+        <v>4.409114690439337</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.364269456004572</v>
+        <v>5.046183199828605</v>
       </c>
       <c r="C2" t="n">
-        <v>4.323616889502953</v>
+        <v>3.371321616383547</v>
       </c>
       <c r="D2" t="n">
-        <v>27.67448603501334</v>
+        <v>26.91068632110932</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.63218876827272</v>
+        <v>19.76749002500953</v>
       </c>
       <c r="C3" t="n">
-        <v>25.83959957577605</v>
+        <v>19.50241814486289</v>
       </c>
       <c r="D3" t="n">
-        <v>61.14815575901258</v>
+        <v>77.86241042381454</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.28218786394211</v>
+        <v>29.41806995775567</v>
       </c>
       <c r="C4" t="n">
-        <v>53.39922112939251</v>
+        <v>43.92928277422778</v>
       </c>
       <c r="D4" t="n">
-        <v>49.12370987739765</v>
+        <v>80.77525586231482</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.99868376159304</v>
+        <v>30.58144098728815</v>
       </c>
       <c r="C5" t="n">
-        <v>51.32086123950202</v>
+        <v>66.66066911835844</v>
       </c>
       <c r="D5" t="n">
-        <v>33.96847056693964</v>
+        <v>50.36365722786139</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.18495378349268</v>
+        <v>21.77614582789851</v>
       </c>
       <c r="C6" t="n">
-        <v>55.58753676215866</v>
+        <v>59.77370897306707</v>
       </c>
       <c r="D6" t="n">
-        <v>32.4428346345401</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.13890945238431</v>
+        <v>10.71970318267092</v>
       </c>
       <c r="C7" t="n">
-        <v>40.78278138211675</v>
+        <v>38.80652325346792</v>
       </c>
       <c r="D7" t="n">
-        <v>33.53650157707104</v>
+        <v>33.23706852727577</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>25.11801501315464</v>
+        <v>23.03180114163017</v>
       </c>
       <c r="D8" t="n">
-        <v>31.87734795689393</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6185,7 +6185,7 @@
         <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -6199,7 +6199,7 @@
         <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.20021977840412</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.29549989217298</v>
+        <v>7.276006127177922</v>
       </c>
       <c r="C21" t="n">
-        <v>77.51468635433791</v>
+        <v>75.48856356947095</v>
       </c>
       <c r="D21" t="n">
-        <v>6.383562405651357</v>
+        <v>5.457004595383442</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.724169952835651</v>
+        <v>4.241150082346221</v>
       </c>
       <c r="C2" t="n">
-        <v>6.379396582195774</v>
+        <v>3.437098712568083</v>
       </c>
       <c r="D2" t="n">
-        <v>23.11328620108265</v>
+        <v>23.30178176029805</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.2359636063845</v>
+        <v>18.47649179392497</v>
       </c>
       <c r="C3" t="n">
-        <v>20.29763378530281</v>
+        <v>15.62942345160922</v>
       </c>
       <c r="D3" t="n">
-        <v>69.10031216341176</v>
+        <v>81.32307108128454</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.81746134693488</v>
+        <v>34.48486985937346</v>
       </c>
       <c r="C4" t="n">
-        <v>59.70400488606553</v>
+        <v>46.85194568977053</v>
       </c>
       <c r="D4" t="n">
-        <v>68.24226466990004</v>
+        <v>101.6678287563912</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.87091769132071</v>
+        <v>38.38633523605029</v>
       </c>
       <c r="C5" t="n">
-        <v>79.32521450314229</v>
+        <v>75.00552460445633</v>
       </c>
       <c r="D5" t="n">
-        <v>44.54680208019903</v>
+        <v>67.49515466696822</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.61013265488955</v>
+        <v>32.36233132279187</v>
       </c>
       <c r="C6" t="n">
-        <v>70.56115274733101</v>
+        <v>84.64923230327274</v>
       </c>
       <c r="D6" t="n">
-        <v>35.90447703971436</v>
+        <v>44.47807974090175</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.4213339960379</v>
+        <v>19.10382857693868</v>
       </c>
       <c r="C7" t="n">
-        <v>63.36003333668064</v>
+        <v>65.27640485537042</v>
       </c>
       <c r="D7" t="n">
-        <v>35.93196597543326</v>
+        <v>36.29128563518759</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.346238144429634</v>
+        <v>9.012443924985718</v>
       </c>
       <c r="C8" t="n">
-        <v>41.55738032076748</v>
+        <v>38.80357801035517</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>28.06718511671205</v>
+        <v>26.84687272033327</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -6510,7 +6510,7 @@
         <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6577,7 +6577,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
         <v>27.27884171020187</v>
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.511138405600343</v>
+        <v>7.485926549101935</v>
       </c>
       <c r="C21" t="n">
-        <v>87.31698396510397</v>
+        <v>84.21667367739677</v>
       </c>
       <c r="D21" t="n">
-        <v>7.511138405600343</v>
+        <v>6.550185730464193</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_59_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_59_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497635938983</v>
+        <v>10.84497630718383</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907203659937</v>
+        <v>37.78907185468874</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.022040417849935</v>
+        <v>1.076977231558751</v>
       </c>
       <c r="C2" t="n">
-        <v>6.763259934556276</v>
+        <v>2.465168485363741</v>
       </c>
       <c r="D2" t="n">
-        <v>21.58372327786612</v>
+        <v>12.63901994447344</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.30192062901829</v>
+        <v>9.056622571676826</v>
       </c>
       <c r="C3" t="n">
-        <v>14.30897278939726</v>
+        <v>35.14656781203581</v>
       </c>
       <c r="D3" t="n">
-        <v>80.94509821514953</v>
+        <v>58.57597677388594</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.27615850899639</v>
+        <v>17.29348581030757</v>
       </c>
       <c r="C4" t="n">
-        <v>42.58919715793088</v>
+        <v>103.0206770928433</v>
       </c>
       <c r="D4" t="n">
-        <v>118.5911956821977</v>
+        <v>70.25877445442299</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.0622196249286</v>
+        <v>18.48140053244621</v>
       </c>
       <c r="C5" t="n">
-        <v>80.40513697781378</v>
+        <v>102.0035864712436</v>
       </c>
       <c r="D5" t="n">
-        <v>87.54735152620933</v>
+        <v>46.68210333693584</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.62650357069227</v>
+        <v>13.4038014060817</v>
       </c>
       <c r="C6" t="n">
-        <v>102.8832324142488</v>
+        <v>59.4516957260741</v>
       </c>
       <c r="D6" t="n">
-        <v>54.21898046243861</v>
+        <v>30.14849024971531</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.80545939030566</v>
+        <v>6.707300315414209</v>
       </c>
       <c r="C7" t="n">
-        <v>94.92027678510286</v>
+        <v>34.43480072645687</v>
       </c>
       <c r="D7" t="n">
-        <v>40.8426679920758</v>
+        <v>29.34443887993716</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.85384276525424</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>62.92021036517807</v>
+        <v>28.37250865273282</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>30.87596529856218</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.543749359432489</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>38.162496759482</v>
+        <v>32.28280975874785</v>
       </c>
       <c r="D9" t="n">
-        <v>34.50155957034565</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>38.43542262126263</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.68357681501636</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93.16336888207336</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.68357681501636</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.919758730159019</v>
+        <v>1.355793579564845</v>
       </c>
       <c r="C2" t="n">
-        <v>10.41830663746715</v>
+        <v>10.06684095934679</v>
       </c>
       <c r="D2" t="n">
-        <v>28.74557278034661</v>
+        <v>15.06884551248429</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.17215000560846</v>
+        <v>6.155558105627501</v>
       </c>
       <c r="C3" t="n">
-        <v>20.52343575727957</v>
+        <v>19.98838325846506</v>
       </c>
       <c r="D3" t="n">
-        <v>79.17304360898402</v>
+        <v>55.095681162331</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.8895298399724</v>
+        <v>17.67636741496382</v>
       </c>
       <c r="C4" t="n">
-        <v>39.05392367493812</v>
+        <v>94.39307826792232</v>
       </c>
       <c r="D4" t="n">
-        <v>128.8396599668302</v>
+        <v>83.86383413987529</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.67014243803564</v>
+        <v>22.5311098124643</v>
       </c>
       <c r="C5" t="n">
-        <v>78.6625348027757</v>
+        <v>152.514505854742</v>
       </c>
       <c r="D5" t="n">
-        <v>107.7958979262998</v>
+        <v>61.8255616749429</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.72337779824321</v>
+        <v>19.28054316370311</v>
       </c>
       <c r="C6" t="n">
-        <v>115.2002391117292</v>
+        <v>114.2341993707504</v>
       </c>
       <c r="D6" t="n">
-        <v>66.65674212754145</v>
+        <v>37.27303333943441</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.98618308334508</v>
+        <v>10.95924962250714</v>
       </c>
       <c r="C7" t="n">
-        <v>120.1325395778652</v>
+        <v>61.20411537815465</v>
       </c>
       <c r="D7" t="n">
-        <v>46.65166915810418</v>
+        <v>31.4404702285041</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.44766125760332</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>93.46238144429634</v>
+        <v>37.63529824230147</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>31.96079651175491</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.09374905798895</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>56.91093266748334</v>
+        <v>35.16718451382499</v>
       </c>
       <c r="D9" t="n">
-        <v>36.0546844384641</v>
+        <v>36.38749691020377</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>37.86600895279948</v>
+        <v>35.44600086183109</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>39.28954312395736</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>34.47308888692249</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.8092064546734</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>28.09761929554372</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>36.94316611080748</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.52772260099505</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>50.2949348885641</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>47.54309607356029</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.867998190106801</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>101.3004766976251</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.851497963870152</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.359000864584843</v>
+        <v>0.7107853378746907</v>
       </c>
       <c r="C2" t="n">
-        <v>15.83853571261379</v>
+        <v>4.060508504764808</v>
       </c>
       <c r="D2" t="n">
-        <v>28.57867567062465</v>
+        <v>10.15028951420777</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.79479903427919</v>
+        <v>6.091744504851459</v>
       </c>
       <c r="C3" t="n">
-        <v>30.0267535343887</v>
+        <v>31.25884690321844</v>
       </c>
       <c r="D3" t="n">
-        <v>82.24100518475531</v>
+        <v>56.18542111404496</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.06820792214531</v>
+        <v>19.29723287467531</v>
       </c>
       <c r="C4" t="n">
-        <v>44.69504598354029</v>
+        <v>85.28049607710342</v>
       </c>
       <c r="D4" t="n">
-        <v>136.7397837429043</v>
+        <v>92.17236496091604</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.79286090106649</v>
+        <v>23.4392264388926</v>
       </c>
       <c r="C5" t="n">
-        <v>74.71100029318228</v>
+        <v>179.3653055658923</v>
       </c>
       <c r="D5" t="n">
-        <v>123.6265796572796</v>
+        <v>70.63674732055802</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.32464936159877</v>
+        <v>15.45663585566179</v>
       </c>
       <c r="C6" t="n">
-        <v>118.8228881404</v>
+        <v>151.225471119066</v>
       </c>
       <c r="D6" t="n">
-        <v>81.63035811271381</v>
+        <v>37.99756314516856</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>48.62792728675301</v>
+        <v>4.611268966847268</v>
       </c>
       <c r="C7" t="n">
-        <v>141.6318325531661</v>
+        <v>61.02445554827749</v>
       </c>
       <c r="D7" t="n">
-        <v>52.87987659384594</v>
+        <v>33.11729530735765</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>30.95941385342316</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>122.1686843164731</v>
+        <v>39.55461500410399</v>
       </c>
       <c r="D8" t="n">
-        <v>41.64082887562846</v>
+        <v>36.38356991938679</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.97499864350409</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>83.20311793491715</v>
+        <v>27.06874770149305</v>
       </c>
       <c r="D9" t="n">
-        <v>37.16405934426299</v>
+        <v>41.3796839862988</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>50.53546307610457</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>37.13853390395258</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.69925071179776</v>
+        <v>17.95125677215293</v>
       </c>
       <c r="D13" t="n">
-        <v>33.82120841130262</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>14.05273663858884</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>43.44429940832985</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>41.1990424087174</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>19.25796296650543</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.038072354452506</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109.5187358294154</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10.04759044306563</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.388052385084748</v>
+        <v>0.7431830121148354</v>
       </c>
       <c r="C2" t="n">
-        <v>10.64312686173967</v>
+        <v>6.096653243372693</v>
       </c>
       <c r="D2" t="n">
-        <v>23.26545709524092</v>
+        <v>8.363508692478577</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.94620916491145</v>
+        <v>4.187153958612646</v>
       </c>
       <c r="C3" t="n">
-        <v>45.7248993252952</v>
+        <v>22.45747873464579</v>
       </c>
       <c r="D3" t="n">
-        <v>92.58371724899546</v>
+        <v>51.39940105584176</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.43235420496287</v>
+        <v>15.76195939168254</v>
       </c>
       <c r="C4" t="n">
-        <v>62.60114236129786</v>
+        <v>82.16639235923255</v>
       </c>
       <c r="D4" t="n">
-        <v>134.3914432343459</v>
+        <v>99.19186104628074</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.83946070705581</v>
+        <v>26.60536278508857</v>
       </c>
       <c r="C5" t="n">
-        <v>70.98035901704441</v>
+        <v>169.523284830818</v>
       </c>
       <c r="D5" t="n">
-        <v>83.17857424231102</v>
+        <v>87.5718952188155</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.18874190558942</v>
+        <v>22.82268888062561</v>
       </c>
       <c r="C6" t="n">
-        <v>93.26308666033425</v>
+        <v>221.2231006841593</v>
       </c>
       <c r="D6" t="n">
-        <v>34.81768233111314</v>
+        <v>49.42903341341842</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.48122060599696</v>
+        <v>9.941177253203202</v>
       </c>
       <c r="C7" t="n">
-        <v>85.87739868128548</v>
+        <v>136.0623778269739</v>
       </c>
       <c r="D7" t="n">
-        <v>29.2845522699781</v>
+        <v>36.53083207502382</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>61.33468782281948</v>
+        <v>58.99812828671206</v>
       </c>
       <c r="D8" t="n">
-        <v>27.37112599440107</v>
+        <v>37.55184968744049</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>38.49530923122167</v>
+        <v>37.27499683484289</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>42.04530892977813</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>29.04009709162065</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>28.89774367450487</v>
+        <v>32.45657910239955</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>28.07602084605028</v>
+        <v>31.45225120095506</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>27.55471281509523</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>48.16650586575701</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.58662746324986</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.091343594223958</v>
+        <v>0.377972866135022</v>
       </c>
       <c r="C2" t="n">
-        <v>4.290237467558561</v>
+        <v>3.723769042208152</v>
       </c>
       <c r="D2" t="n">
-        <v>16.11047982669016</v>
+        <v>6.528622233241289</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.56747553525044</v>
+        <v>3.499930565639879</v>
       </c>
       <c r="C3" t="n">
-        <v>44.52225838759285</v>
+        <v>23.67484588791183</v>
       </c>
       <c r="D3" t="n">
-        <v>90.47786842338604</v>
+        <v>47.13370728088937</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.11475097487241</v>
+        <v>13.0052118381575</v>
       </c>
       <c r="C4" t="n">
-        <v>89.5687700492535</v>
+        <v>71.63714823118551</v>
       </c>
       <c r="D4" t="n">
-        <v>149.208961334543</v>
+        <v>102.4080665253933</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.05468443846411</v>
+        <v>27.36621725587985</v>
       </c>
       <c r="C5" t="n">
-        <v>93.7569057555704</v>
+        <v>167.6334205001429</v>
       </c>
       <c r="D5" t="n">
-        <v>104.1143440353743</v>
+        <v>100.4573338370549</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.22649028670731</v>
+        <v>27.45162930614931</v>
       </c>
       <c r="C6" t="n">
-        <v>107.1499079369054</v>
+        <v>251.0093260310076</v>
       </c>
       <c r="D6" t="n">
-        <v>45.16235789076178</v>
+        <v>60.17622553180826</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.22360179685679</v>
+        <v>11.13890945238431</v>
       </c>
       <c r="C7" t="n">
-        <v>107.0772586067911</v>
+        <v>203.9737935205428</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>40.00425545264903</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.346238144429634</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>80.77820110542756</v>
+        <v>92.87824156026949</v>
       </c>
       <c r="D8" t="n">
-        <v>28.53940576245478</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>44.26405874137593</v>
+        <v>48.14687091167205</v>
       </c>
       <c r="D9" t="n">
-        <v>28.28906009787183</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>32.02951885105219</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>28.07602084605028</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.47965802121596</v>
+        <v>23.43235420496287</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>40.91826256530281</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.499349728563132</v>
+        <v>1.20951317163207</v>
       </c>
       <c r="C2" t="n">
-        <v>5.329908286355933</v>
+        <v>5.955281573961152</v>
       </c>
       <c r="D2" t="n">
-        <v>20.23480193223101</v>
+        <v>13.52553812140831</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.58019719767664</v>
+        <v>2.390555659840983</v>
       </c>
       <c r="C3" t="n">
-        <v>29.6095107600838</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D3" t="n">
-        <v>82.82023633026093</v>
+        <v>41.99425804915732</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.08694324398402</v>
+        <v>9.929396280752242</v>
       </c>
       <c r="C4" t="n">
-        <v>100.7744383455266</v>
+        <v>65.2047372729604</v>
       </c>
       <c r="D4" t="n">
-        <v>159.5340019401067</v>
+        <v>102.573981887411</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.34416114249668</v>
+        <v>24.47006152835176</v>
       </c>
       <c r="C5" t="n">
-        <v>129.4679784975481</v>
+        <v>151.7045639987384</v>
       </c>
       <c r="D5" t="n">
-        <v>130.7687942056752</v>
+        <v>112.2137625954105</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.62650357069227</v>
+        <v>31.91956310817655</v>
       </c>
       <c r="C6" t="n">
-        <v>128.6040405178109</v>
+        <v>259.1401605175796</v>
       </c>
       <c r="D6" t="n">
-        <v>63.83912621635311</v>
+        <v>74.42531171124647</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.86534600026472</v>
+        <v>19.64280806657018</v>
       </c>
       <c r="C7" t="n">
-        <v>131.1516758103314</v>
+        <v>278.9518291892802</v>
       </c>
       <c r="D7" t="n">
-        <v>37.00992495469625</v>
+        <v>46.35223610830891</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.85246010692249</v>
+        <v>7.34347282776614</v>
       </c>
       <c r="C8" t="n">
-        <v>109.6514010873262</v>
+        <v>170.5688461358408</v>
       </c>
       <c r="D8" t="n">
-        <v>30.70906818884022</v>
+        <v>41.8911745402114</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.323436963053704</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>68.78124415953151</v>
+        <v>76.54686850012379</v>
       </c>
       <c r="D9" t="n">
-        <v>29.06562253193106</v>
+        <v>42.71093387325747</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>41.28249096357838</v>
+        <v>43.2754388031994</v>
       </c>
       <c r="D10" t="n">
-        <v>30.46363126277853</v>
+        <v>35.73070769606267</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.8884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>33.22921454564179</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>26.03594911662541</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>41.74489413227862</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.651700549170635</v>
+        <v>0.8119053514121122</v>
       </c>
       <c r="C2" t="n">
-        <v>2.453387512912779</v>
+        <v>3.09643225919444</v>
       </c>
       <c r="D2" t="n">
-        <v>14.005612748785</v>
+        <v>9.737955478424112</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.94206118991621</v>
+        <v>3.848451000647497</v>
       </c>
       <c r="C3" t="n">
-        <v>27.64110661306895</v>
+        <v>23.26251185212817</v>
       </c>
       <c r="D3" t="n">
-        <v>82.88404993103697</v>
+        <v>47.21224709722911</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.66875977970388</v>
+        <v>16.56601076146068</v>
       </c>
       <c r="C4" t="n">
-        <v>100.3532685804047</v>
+        <v>90.23243149732434</v>
       </c>
       <c r="D4" t="n">
-        <v>168.3402788472006</v>
+        <v>107.4748664270111</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.62672455487052</v>
+        <v>19.78221624057323</v>
       </c>
       <c r="C5" t="n">
-        <v>163.4609927570939</v>
+        <v>222.3413113192964</v>
       </c>
       <c r="D5" t="n">
-        <v>140.2426595516569</v>
+        <v>104.2861498836175</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.62271544859552</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="C6" t="n">
-        <v>158.7122791116522</v>
+        <v>249.7615246989099</v>
       </c>
       <c r="D6" t="n">
-        <v>61.50453017565419</v>
+        <v>63.83912621635311</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.162651323735481</v>
+        <v>4.850815406683489</v>
       </c>
       <c r="C7" t="n">
-        <v>141.0928530635346</v>
+        <v>119.952879747988</v>
       </c>
       <c r="D7" t="n">
-        <v>36.83026512481909</v>
+        <v>36.23139902522853</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.339324852770902</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C8" t="n">
-        <v>85.03407740333748</v>
+        <v>56.41122308602172</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>31.50624732468863</v>
+        <v>32.9484347022272</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>26.33538216642069</v>
+        <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>26.05067533218912</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.7904711328347</v>
+        <v>21.32356013624072</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.04880964777186</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>35.1171153809084</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.353650157707104</v>
+        <v>0.3809181092477624</v>
       </c>
       <c r="C2" t="n">
-        <v>2.484803439448677</v>
+        <v>2.76067454434203</v>
       </c>
       <c r="D2" t="n">
-        <v>17.48394486493144</v>
+        <v>6.619924769736242</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.66869335977909</v>
+        <v>3.333033455917922</v>
       </c>
       <c r="C3" t="n">
-        <v>18.27032477603314</v>
+        <v>17.24930716361646</v>
       </c>
       <c r="D3" t="n">
-        <v>75.56512079587699</v>
+        <v>44.03629327399068</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.42252103238718</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C4" t="n">
-        <v>85.54851320036282</v>
+        <v>70.37363893581986</v>
       </c>
       <c r="D4" t="n">
-        <v>170.9183483185527</v>
+        <v>102.4846428463245</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.76956099807182</v>
+        <v>17.96598298771663</v>
       </c>
       <c r="C5" t="n">
-        <v>173.3766445699867</v>
+        <v>176.6164119940012</v>
       </c>
       <c r="D5" t="n">
-        <v>165.4981192434061</v>
+        <v>106.2251015995049</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.80638438474769</v>
+        <v>11.87423848286517</v>
       </c>
       <c r="C6" t="n">
-        <v>207.5375376869588</v>
+        <v>248.0307034963227</v>
       </c>
       <c r="D6" t="n">
-        <v>83.32092765942681</v>
+        <v>67.98504677138737</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.30156077611979</v>
+        <v>4.19206269713388</v>
       </c>
       <c r="C7" t="n">
-        <v>180.5581290265521</v>
+        <v>163.0113523085489</v>
       </c>
       <c r="D7" t="n">
-        <v>43.77711188006952</v>
+        <v>34.6743471662931</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.9248473951295</v>
+        <v>1.251728322914683</v>
       </c>
       <c r="C8" t="n">
-        <v>129.0114658150733</v>
+        <v>64.58918146239766</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>27.28767743954009</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>58.46405753560178</v>
+        <v>30.39687241888974</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>21.74374815365835</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>18.79065105928395</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.52209415667683</v>
+        <v>13.68261775408779</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>17.76963344686726</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.581996462169111</v>
+        <v>0.4368777283898306</v>
       </c>
       <c r="C2" t="n">
-        <v>1.604175748739288</v>
+        <v>5.385867905498002</v>
       </c>
       <c r="D2" t="n">
-        <v>13.38416645199677</v>
+        <v>10.37805498159303</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.03899217072939</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C3" t="n">
-        <v>14.56913593102267</v>
+        <v>13.30268139254428</v>
       </c>
       <c r="D3" t="n">
-        <v>72.87513208624073</v>
+        <v>39.11282853719293</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.54716193309751</v>
+        <v>8.729700586162638</v>
       </c>
       <c r="C4" t="n">
-        <v>70.52679157768236</v>
+        <v>55.12218835034566</v>
       </c>
       <c r="D4" t="n">
-        <v>170.7907211170006</v>
+        <v>101.6678287563912</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.73367830137119</v>
+        <v>17.94143929511046</v>
       </c>
       <c r="C5" t="n">
-        <v>171.5113239319178</v>
+        <v>150.7473599870978</v>
       </c>
       <c r="D5" t="n">
-        <v>182.4332671416635</v>
+        <v>119.5523266846554</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.93721887131977</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="C6" t="n">
-        <v>240.5841471596107</v>
+        <v>269.2433261419836</v>
       </c>
       <c r="D6" t="n">
-        <v>100.1863714706828</v>
+        <v>85.37376210900689</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.04394196697963</v>
+        <v>8.982991493858314</v>
       </c>
       <c r="C7" t="n">
-        <v>225.5329731058027</v>
+        <v>265.8965482182061</v>
       </c>
       <c r="D7" t="n">
-        <v>50.18497914568845</v>
+        <v>45.39405034896402</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>2.670353755551324</v>
       </c>
       <c r="C8" t="n">
-        <v>163.7260646372405</v>
+        <v>143.1977201414398</v>
       </c>
       <c r="D8" t="n">
-        <v>35.21529015133309</v>
+        <v>30.29182541453534</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.7765624340592268</v>
       </c>
       <c r="C9" t="n">
-        <v>68.33749419721195</v>
+        <v>55.91249525226433</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>23.85156047467625</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>20.64124548178919</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.98900515327081</v>
+        <v>17.59193711239859</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>18.48041878474196</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>13.4519070435898</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.829797794266807</v>
+        <v>1.013163630782708</v>
       </c>
       <c r="C2" t="n">
-        <v>7.178539213452678</v>
+        <v>10.8973995171396</v>
       </c>
       <c r="D2" t="n">
-        <v>20.64517247260617</v>
+        <v>11.63763728614169</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.45699570856028</v>
+        <v>1.826050729899067</v>
       </c>
       <c r="C3" t="n">
-        <v>10.57833151325938</v>
+        <v>17.50456156672063</v>
       </c>
       <c r="D3" t="n">
-        <v>67.49515466696822</v>
+        <v>38.2587080344982</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.30619177720055</v>
+        <v>6.44517367838031</v>
       </c>
       <c r="C4" t="n">
-        <v>54.95627298832795</v>
+        <v>43.32943492693298</v>
       </c>
       <c r="D4" t="n">
-        <v>168.2892279665797</v>
+        <v>97.59652102687967</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>61.99736752318609</v>
+        <v>15.9288565014045</v>
       </c>
       <c r="C5" t="n">
-        <v>153.1280981698963</v>
+        <v>125.271007061893</v>
       </c>
       <c r="D5" t="n">
-        <v>194.7542008299611</v>
+        <v>129.0261920306371</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>65.77120569831082</v>
+        <v>21.41388092503143</v>
       </c>
       <c r="C6" t="n">
-        <v>254.5112200920559</v>
+        <v>255.8395247359018</v>
       </c>
       <c r="D6" t="n">
-        <v>125.6254179831261</v>
+        <v>102.2392059202628</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.49468733641593</v>
+        <v>14.97165248976386</v>
       </c>
       <c r="C7" t="n">
-        <v>276.0173853012865</v>
+        <v>329.1368083349686</v>
       </c>
       <c r="D7" t="n">
-        <v>62.22218774745859</v>
+        <v>57.25159912085699</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.846929473595507</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>219.8034935038184</v>
+        <v>245.5890969558608</v>
       </c>
       <c r="D8" t="n">
-        <v>38.88702656521616</v>
+        <v>35.13184159647211</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>118.7031149204818</v>
+        <v>113.8218653349667</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>25.95937279569415</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>49.53898915629405</v>
+        <v>45.41074005993622</v>
       </c>
       <c r="D10" t="n">
-        <v>26.76244241776806</v>
+        <v>21.78007281871549</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>23.98900515327081</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>19.01350778814797</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>8.600109889202059</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.391758391723482</v>
+        <v>5.962153807890879</v>
       </c>
       <c r="C2" t="n">
-        <v>5.561600744558181</v>
+        <v>5.716716881829178</v>
       </c>
       <c r="D2" t="n">
-        <v>13.15051049838602</v>
+        <v>6.213481220178063</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.71158715912969</v>
+        <v>1.560978849752428</v>
       </c>
       <c r="C2" t="n">
-        <v>4.077198215737003</v>
+        <v>11.5119735799981</v>
       </c>
       <c r="D2" t="n">
-        <v>15.19450921862788</v>
+        <v>12.30522572502952</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.75705065316131</v>
+        <v>2.577087723647877</v>
       </c>
       <c r="C3" t="n">
-        <v>17.36220814960484</v>
+        <v>29.92857876396402</v>
       </c>
       <c r="D3" t="n">
-        <v>75.74674412116266</v>
+        <v>38.39615271309275</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.29864089520283</v>
+        <v>5.002986300841745</v>
       </c>
       <c r="C4" t="n">
-        <v>80.11159441424397</v>
+        <v>43.44429940832985</v>
       </c>
       <c r="D4" t="n">
-        <v>173.572994110836</v>
+        <v>94.92911251444107</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.75449062514284</v>
+        <v>13.22905031472577</v>
       </c>
       <c r="C5" t="n">
-        <v>220.107835292135</v>
+        <v>103.7216449536755</v>
       </c>
       <c r="D5" t="n">
-        <v>179.610742491954</v>
+        <v>134.1067364001143</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.41388092503143</v>
+        <v>21.81639748377262</v>
       </c>
       <c r="C6" t="n">
-        <v>234.1841338756257</v>
+        <v>229.1526768913608</v>
       </c>
       <c r="D6" t="n">
-        <v>97.20774893599796</v>
+        <v>115.6027556704704</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.527640485537042</v>
+        <v>19.58292145661112</v>
       </c>
       <c r="C7" t="n">
-        <v>154.567340304322</v>
+        <v>351.175080799901</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>70.60631314172635</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>87.45408549430587</v>
+        <v>330.7066229140593</v>
       </c>
       <c r="D8" t="n">
-        <v>24.95111790343269</v>
+        <v>40.47254910757476</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>37.82968428774233</v>
+        <v>199.1327955909017</v>
       </c>
       <c r="D9" t="n">
-        <v>20.41249826669968</v>
+        <v>28.51093507903161</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>22.63419332141022</v>
+        <v>83.84616268119885</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>22.776546738526</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.34806277111788</v>
+        <v>35.53926689373453</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>19.72429312602266</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
-        <v>13.23494080095125</v>
+        <v>15.62156946997525</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>10.14636252339079</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>11.46681318560274</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.413757751844412</v>
+        <v>4.269620765769378</v>
       </c>
       <c r="C2" t="n">
-        <v>6.027930904075415</v>
+        <v>7.163812997888975</v>
       </c>
       <c r="D2" t="n">
-        <v>28.75833550050182</v>
+        <v>22.55270826195773</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.45699570856028</v>
+        <v>9.842020735074275</v>
       </c>
       <c r="C3" t="n">
-        <v>14.01444847812322</v>
+        <v>11.28518986031709</v>
       </c>
       <c r="D3" t="n">
-        <v>14.18134558784518</v>
+        <v>7.299294181075036</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39786395711344</v>
+        <v>11.6786428045387</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14175836371153</v>
+        <v>59.95036639663201</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576219289072169</v>
+        <v>0.7785761869692468</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.355433726666351</v>
+        <v>2.423935081785375</v>
       </c>
       <c r="C2" t="n">
-        <v>4.236241343824987</v>
+        <v>6.665085164131596</v>
       </c>
       <c r="D2" t="n">
-        <v>23.29196428325557</v>
+        <v>18.87017262332794</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.86289947877071</v>
+        <v>13.07687942056751</v>
       </c>
       <c r="C3" t="n">
-        <v>19.95402208881642</v>
+        <v>22.41330008795468</v>
       </c>
       <c r="D3" t="n">
-        <v>34.91094836301658</v>
+        <v>25.30945581548277</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.37533072265855</v>
+        <v>12.13734686760332</v>
       </c>
       <c r="C4" t="n">
-        <v>21.91359050649305</v>
+        <v>18.91435127001905</v>
       </c>
       <c r="D4" t="n">
-        <v>22.50067563363265</v>
+        <v>17.99543541884404</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.50089661781091</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.433973543006096</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43870843234517</v>
+        <v>13.63025695444608</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13174178045205</v>
+        <v>73.7637435181788</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250254406809511</v>
+        <v>1.603559641699539</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.433973543006096</v>
+        <v>2.842159603794516</v>
       </c>
       <c r="C2" t="n">
-        <v>6.947828502954677</v>
+        <v>4.914629007459533</v>
       </c>
       <c r="D2" t="n">
-        <v>32.79233681725196</v>
+        <v>15.01288589334223</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.25559856046944</v>
+        <v>10.38689071093125</v>
       </c>
       <c r="C3" t="n">
-        <v>17.84817326320701</v>
+        <v>24.75476836258332</v>
       </c>
       <c r="D3" t="n">
-        <v>45.44510122958485</v>
+        <v>35.0434843030899</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.4233385491754</v>
+        <v>20.22891144600553</v>
       </c>
       <c r="C4" t="n">
-        <v>38.4285503873329</v>
+        <v>42.32118003467151</v>
       </c>
       <c r="D4" t="n">
-        <v>34.91880234465055</v>
+        <v>27.08249216935251</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.83005983617407</v>
+        <v>11.09374905798896</v>
       </c>
       <c r="C5" t="n">
-        <v>25.40272184738622</v>
+        <v>23.26742059064941</v>
       </c>
       <c r="D5" t="n">
-        <v>30.75324683553134</v>
+        <v>26.21266370338984</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.13430381349934</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>24.03318379996192</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>24.18437294641592</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>42.09145107187774</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73060901068245</v>
+        <v>14.84296579888781</v>
       </c>
       <c r="C21" t="n">
-        <v>102.056714965163</v>
+        <v>87.40857637122818</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182652252670612</v>
+        <v>2.473827633147967</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.313218575383737</v>
+        <v>1.872192871998667</v>
       </c>
       <c r="C2" t="n">
-        <v>4.092906179004952</v>
+        <v>6.198755004614362</v>
       </c>
       <c r="D2" t="n">
-        <v>35.26241404113694</v>
+        <v>17.26305163147591</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.61393647251952</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C3" t="n">
-        <v>23.10052348092745</v>
+        <v>21.29901644363455</v>
       </c>
       <c r="D3" t="n">
-        <v>60.25967408666923</v>
+        <v>38.92138773486479</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.51566389110361</v>
+        <v>20.45864040879928</v>
       </c>
       <c r="C4" t="n">
-        <v>41.91277298970483</v>
+        <v>54.1266961782394</v>
       </c>
       <c r="D4" t="n">
-        <v>49.03437083631119</v>
+        <v>38.2881604656256</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.86276061005048</v>
+        <v>21.32846887476196</v>
       </c>
       <c r="C5" t="n">
-        <v>49.99550183876883</v>
+        <v>55.12513359345841</v>
       </c>
       <c r="D5" t="n">
-        <v>35.80924751240241</v>
+        <v>30.36054775383262</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.06920536538279</v>
+        <v>10.14341728027805</v>
       </c>
       <c r="C6" t="n">
-        <v>26.64659618866693</v>
+        <v>25.19753657719864</v>
       </c>
       <c r="D6" t="n">
-        <v>38.44033135978387</v>
+        <v>33.65038431076368</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.13997331554657</v>
+        <v>17.54677671800324</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.62700229231099</v>
+        <v>25.86905200690345</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>27.95624762613216</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>27.75891633757857</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>28.07602084605028</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>43.39324852770902</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05319600065912</v>
+        <v>16.09051622260752</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7756120043</v>
+        <v>101.6243129848896</v>
       </c>
       <c r="D21" t="n">
-        <v>6.017732000219707</v>
+        <v>3.38747709949632</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.235079669671493</v>
+        <v>1.700387023755476</v>
       </c>
       <c r="C2" t="n">
-        <v>5.228788272818512</v>
+        <v>9.664324400605601</v>
       </c>
       <c r="D2" t="n">
-        <v>30.13769102496859</v>
+        <v>22.22873151955628</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.35591675275186</v>
+        <v>8.069966128908781</v>
       </c>
       <c r="C3" t="n">
-        <v>17.81872083207961</v>
+        <v>22.92380889416302</v>
       </c>
       <c r="D3" t="n">
-        <v>69.29175296573987</v>
+        <v>43.38343105066655</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.47889725768997</v>
+        <v>20.15233512507428</v>
       </c>
       <c r="C4" t="n">
-        <v>42.52538355715484</v>
+        <v>53.6800009728071</v>
       </c>
       <c r="D4" t="n">
-        <v>58.6191736728728</v>
+        <v>48.23031946653305</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.50027472300515</v>
+        <v>26.43355693684537</v>
       </c>
       <c r="C5" t="n">
-        <v>47.73748211900116</v>
+        <v>79.81608835526569</v>
       </c>
       <c r="D5" t="n">
-        <v>36.00559705325178</v>
+        <v>37.3064127613788</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.15600007398401</v>
+        <v>19.56230475482195</v>
       </c>
       <c r="C6" t="n">
-        <v>36.70951015719674</v>
+        <v>57.84162949110934</v>
       </c>
       <c r="D6" t="n">
-        <v>31.87931145230244</v>
+        <v>35.94472869558847</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.509568116233099</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>19.28348840681585</v>
+        <v>27.66761380108361</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>36.65060529494193</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>30.95155987178918</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.2734342500619</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.40659208494097</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.054583504702939</v>
+        <v>17.36686161116801</v>
       </c>
       <c r="C21" t="n">
-        <v>66.13672035659006</v>
+        <v>115.4896297142673</v>
       </c>
       <c r="D21" t="n">
-        <v>4.409114690439337</v>
+        <v>4.341715402792002</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.046183199828605</v>
+        <v>2.199114857512855</v>
       </c>
       <c r="C2" t="n">
-        <v>3.371321616383547</v>
+        <v>10.45659479793278</v>
       </c>
       <c r="D2" t="n">
-        <v>26.91068632110932</v>
+        <v>23.5923790807551</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.76749002500953</v>
+        <v>6.837872760079034</v>
       </c>
       <c r="C3" t="n">
-        <v>19.50241814486289</v>
+        <v>30.99377502307181</v>
       </c>
       <c r="D3" t="n">
-        <v>77.86241042381454</v>
+        <v>50.15258147144831</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.41806995775567</v>
+        <v>17.82952005682632</v>
       </c>
       <c r="C4" t="n">
-        <v>43.92928277422778</v>
+        <v>55.632697156554</v>
       </c>
       <c r="D4" t="n">
-        <v>80.77525586231482</v>
+        <v>57.45776613874882</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.58144098728815</v>
+        <v>28.34796496012666</v>
       </c>
       <c r="C5" t="n">
-        <v>66.66066911835844</v>
+        <v>89.82991493858316</v>
       </c>
       <c r="D5" t="n">
-        <v>50.36365722786139</v>
+        <v>45.74944301790137</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.77614582789851</v>
+        <v>27.65288758551991</v>
       </c>
       <c r="C6" t="n">
-        <v>59.77370897306707</v>
+        <v>91.73352373711774</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>39.56737772425921</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.71970318267092</v>
+        <v>16.04961146902685</v>
       </c>
       <c r="C7" t="n">
-        <v>38.80652325346792</v>
+        <v>55.69454726192155</v>
       </c>
       <c r="D7" t="n">
-        <v>33.23706852727577</v>
+        <v>38.50709020367265</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>9.179341034707678</v>
       </c>
       <c r="C8" t="n">
-        <v>23.03180114163017</v>
+        <v>31.29320807286708</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>39.13737222979909</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>31.94999728700819</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>39.160934174701</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.398851609831464</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>34.44952694202058</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>34.11769621798515</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>47.26722496866692</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>44.69504598354028</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>43.1870815098172</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>31.03599017435442</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.20021977840412</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.276006127177922</v>
+        <v>18.66524902681058</v>
       </c>
       <c r="C21" t="n">
-        <v>75.48856356947095</v>
+        <v>128.8791004232159</v>
       </c>
       <c r="D21" t="n">
-        <v>5.457004595383442</v>
+        <v>5.332928293374452</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.241150082346221</v>
+        <v>1.968404147014855</v>
       </c>
       <c r="C2" t="n">
-        <v>3.437098712568083</v>
+        <v>6.356816384998097</v>
       </c>
       <c r="D2" t="n">
-        <v>23.30178176029805</v>
+        <v>18.40384246381071</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.47649179392497</v>
+        <v>10.61760142142925</v>
       </c>
       <c r="C3" t="n">
-        <v>15.62942345160922</v>
+        <v>46.77536936883928</v>
       </c>
       <c r="D3" t="n">
-        <v>81.32307108128454</v>
+        <v>56.64684253504096</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.48486985937346</v>
+        <v>13.61782240560751</v>
       </c>
       <c r="C4" t="n">
-        <v>46.85194568977053</v>
+        <v>80.08606897393356</v>
       </c>
       <c r="D4" t="n">
-        <v>101.6678287563912</v>
+        <v>54.91798482786232</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.38633523605029</v>
+        <v>15.56070111231195</v>
       </c>
       <c r="C5" t="n">
-        <v>75.00552460445633</v>
+        <v>54.8060655895782</v>
       </c>
       <c r="D5" t="n">
-        <v>67.49515466696822</v>
+        <v>37.25732537616646</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.36233132279187</v>
+        <v>9.94215900090745</v>
       </c>
       <c r="C6" t="n">
-        <v>84.64923230327274</v>
+        <v>36.66925850132262</v>
       </c>
       <c r="D6" t="n">
-        <v>44.47807974090175</v>
+        <v>25.35854320069512</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.10382857693868</v>
+        <v>6.048547605864599</v>
       </c>
       <c r="C7" t="n">
-        <v>65.27640485537042</v>
+        <v>21.97838585497334</v>
       </c>
       <c r="D7" t="n">
-        <v>36.29128563518759</v>
+        <v>27.48795397120644</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.012443924985718</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>38.80357801035517</v>
+        <v>23.53249247079604</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>28.78975142703771</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>26.84687272033327</v>
+        <v>26.29218526743382</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>37.01188845010476</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
         <v>35.7169632282032</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>24.58296251434014</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.485926549101935</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>84.21667367739677</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.550185730464193</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
